--- a/data/atlas.xlsx
+++ b/data/atlas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SOCIOLOGY\github\websites\mgi_atlas_website\mgi_atlas\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE82C974-E1A2-40B7-AFA9-7C5F54E12FD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA8A8EBB-6963-44CC-85D5-B33225DE1279}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4182" uniqueCount="1098">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2744" uniqueCount="1094">
   <si>
     <t>map_id</t>
   </si>
@@ -1286,12 +1286,6 @@
     <t>00813_02_1950-0145</t>
   </si>
   <si>
-    <t>San Francisco, 1950 (sheet 0145)</t>
-  </si>
-  <si>
-    <t>00813_02_1950-0145.jpg</t>
-  </si>
-  <si>
     <t>00813_02_1950-0161</t>
   </si>
   <si>
@@ -3312,12 +3306,6 @@
   </si>
   <si>
     <t>03573_04_1915-0362</t>
-  </si>
-  <si>
-    <t>i</t>
-  </si>
-  <si>
-    <t>d</t>
   </si>
 </sst>
 </file>
@@ -3686,47 +3674,47 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
     </row>
   </sheetData>
@@ -3751,45 +3739,45 @@
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>827</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>828</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>829</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>830</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>831</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>832</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>833</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="K1" t="s">
         <v>834</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="L1" t="s">
         <v>835</v>
-      </c>
-      <c r="K1" t="s">
-        <v>836</v>
-      </c>
-      <c r="L1" t="s">
-        <v>837</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="B2" t="s">
         <v>283</v>
@@ -3801,21 +3789,21 @@
         <v>-93.243848601079563</v>
       </c>
       <c r="H2" t="s">
+        <v>837</v>
+      </c>
+      <c r="J2" t="s">
+        <v>838</v>
+      </c>
+      <c r="K2" t="s">
         <v>839</v>
       </c>
-      <c r="J2" t="s">
+      <c r="L2" t="s">
         <v>840</v>
-      </c>
-      <c r="K2" t="s">
-        <v>841</v>
-      </c>
-      <c r="L2" t="s">
-        <v>842</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="B3" t="s">
         <v>283</v>
@@ -3827,18 +3815,18 @@
         <v>-93.275968113472459</v>
       </c>
       <c r="H3" t="s">
+        <v>837</v>
+      </c>
+      <c r="K3" t="s">
         <v>839</v>
       </c>
-      <c r="K3" t="s">
-        <v>841</v>
-      </c>
       <c r="L3" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="B4" t="s">
         <v>283</v>
@@ -3850,18 +3838,18 @@
         <v>-93.288981012386159</v>
       </c>
       <c r="H4" t="s">
+        <v>837</v>
+      </c>
+      <c r="K4" t="s">
         <v>839</v>
       </c>
-      <c r="K4" t="s">
-        <v>841</v>
-      </c>
       <c r="L4" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="B5" t="s">
         <v>283</v>
@@ -3873,18 +3861,18 @@
         <v>-93.244822228811913</v>
       </c>
       <c r="H5" t="s">
+        <v>837</v>
+      </c>
+      <c r="K5" t="s">
         <v>839</v>
       </c>
-      <c r="K5" t="s">
-        <v>841</v>
-      </c>
       <c r="L5" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
       <c r="B6" t="s">
         <v>283</v>
@@ -3896,21 +3884,21 @@
         <v>-93.245466422228006</v>
       </c>
       <c r="H6" t="s">
+        <v>837</v>
+      </c>
+      <c r="J6" t="s">
+        <v>845</v>
+      </c>
+      <c r="K6" t="s">
         <v>839</v>
       </c>
-      <c r="J6" t="s">
-        <v>847</v>
-      </c>
-      <c r="K6" t="s">
-        <v>841</v>
-      </c>
       <c r="L6" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="B7" t="s">
         <v>176</v>
@@ -3922,21 +3910,21 @@
         <v>-90.089013384298823</v>
       </c>
       <c r="H7" t="s">
+        <v>837</v>
+      </c>
+      <c r="J7" t="s">
+        <v>847</v>
+      </c>
+      <c r="K7" t="s">
         <v>839</v>
       </c>
-      <c r="J7" t="s">
-        <v>849</v>
-      </c>
-      <c r="K7" t="s">
-        <v>841</v>
-      </c>
       <c r="L7" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>850</v>
+        <v>848</v>
       </c>
       <c r="B8" t="s">
         <v>176</v>
@@ -3948,21 +3936,21 @@
         <v>-90.078527779815644</v>
       </c>
       <c r="H8" t="s">
+        <v>837</v>
+      </c>
+      <c r="J8" t="s">
+        <v>849</v>
+      </c>
+      <c r="K8" t="s">
         <v>839</v>
       </c>
-      <c r="J8" t="s">
-        <v>851</v>
-      </c>
-      <c r="K8" t="s">
-        <v>841</v>
-      </c>
       <c r="L8" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
       <c r="B9" t="s">
         <v>176</v>
@@ -3974,21 +3962,21 @@
         <v>-90.106785474254508</v>
       </c>
       <c r="H9" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="J9" t="s">
+        <v>851</v>
+      </c>
+      <c r="K9" t="s">
+        <v>852</v>
+      </c>
+      <c r="L9" t="s">
         <v>853</v>
-      </c>
-      <c r="K9" t="s">
-        <v>854</v>
-      </c>
-      <c r="L9" t="s">
-        <v>855</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>856</v>
+        <v>854</v>
       </c>
       <c r="B10" t="s">
         <v>176</v>
@@ -4000,21 +3988,21 @@
         <v>-90.053934087901851</v>
       </c>
       <c r="H10" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="J10" t="s">
-        <v>857</v>
+        <v>855</v>
       </c>
       <c r="K10" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="L10" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="B11" t="s">
         <v>10</v>
@@ -4026,18 +4014,18 @@
         <v>-122.2802639125107</v>
       </c>
       <c r="H11" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="K11" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="L11" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="B12" t="s">
         <v>10</v>
@@ -4049,18 +4037,18 @@
         <v>-122.2772225000017</v>
       </c>
       <c r="H12" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="K12" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="L12" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="B13" t="s">
         <v>10</v>
@@ -4072,18 +4060,18 @@
         <v>-122.2831547108984</v>
       </c>
       <c r="H13" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="K13" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="L13" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="B14" t="s">
         <v>10</v>
@@ -4095,18 +4083,18 @@
         <v>-122.2812675192871</v>
       </c>
       <c r="H14" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="K14" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="L14" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="B15" t="s">
         <v>10</v>
@@ -4118,18 +4106,18 @@
         <v>-122.2152269089501</v>
       </c>
       <c r="H15" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="K15" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="L15" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="B16" t="s">
         <v>10</v>
@@ -4141,24 +4129,24 @@
         <v>-122.30496065835619</v>
       </c>
       <c r="H16" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="K16" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="L16" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="B17" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="C17" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
       <c r="E17">
         <v>41.815778899288802</v>
@@ -4167,27 +4155,27 @@
         <v>-71.439371583659494</v>
       </c>
       <c r="H17" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="J17" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
       <c r="K17" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="L17" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
       <c r="B18" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="C18" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
       <c r="E18">
         <v>41.809868141718297</v>
@@ -4196,27 +4184,27 @@
         <v>-71.425628447060205</v>
       </c>
       <c r="H18" t="s">
+        <v>837</v>
+      </c>
+      <c r="J18" t="s">
+        <v>867</v>
+      </c>
+      <c r="K18" t="s">
         <v>839</v>
       </c>
-      <c r="J18" t="s">
-        <v>869</v>
-      </c>
-      <c r="K18" t="s">
-        <v>841</v>
-      </c>
       <c r="L18" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
       <c r="B19" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="C19" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="E19">
         <v>41.822415660229296</v>
@@ -4225,27 +4213,27 @@
         <v>-71.420818266054994</v>
       </c>
       <c r="H19" t="s">
+        <v>837</v>
+      </c>
+      <c r="J19" t="s">
+        <v>870</v>
+      </c>
+      <c r="K19" t="s">
         <v>839</v>
       </c>
-      <c r="J19" t="s">
-        <v>872</v>
-      </c>
-      <c r="K19" t="s">
-        <v>841</v>
-      </c>
       <c r="L19" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>873</v>
+        <v>871</v>
       </c>
       <c r="B20" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="C20" t="s">
-        <v>874</v>
+        <v>872</v>
       </c>
       <c r="E20">
         <v>41.819646005097503</v>
@@ -4254,27 +4242,27 @@
         <v>-71.446628808854797</v>
       </c>
       <c r="H20" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="J20" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="K20" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="L20" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>876</v>
+        <v>874</v>
       </c>
       <c r="B21" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="C21" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="E21">
         <v>41.817970918279897</v>
@@ -4283,27 +4271,27 @@
         <v>-71.399814082462697</v>
       </c>
       <c r="H21" t="s">
+        <v>837</v>
+      </c>
+      <c r="J21" t="s">
+        <v>876</v>
+      </c>
+      <c r="K21" t="s">
         <v>839</v>
       </c>
-      <c r="J21" t="s">
-        <v>878</v>
-      </c>
-      <c r="K21" t="s">
-        <v>841</v>
-      </c>
       <c r="L21" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="B22" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="C22" t="s">
-        <v>880</v>
+        <v>878</v>
       </c>
       <c r="E22">
         <v>41.837088219942302</v>
@@ -4312,27 +4300,27 @@
         <v>-71.414186038766601</v>
       </c>
       <c r="H22" t="s">
+        <v>837</v>
+      </c>
+      <c r="J22" t="s">
+        <v>879</v>
+      </c>
+      <c r="K22" t="s">
         <v>839</v>
       </c>
-      <c r="J22" t="s">
-        <v>881</v>
-      </c>
-      <c r="K22" t="s">
-        <v>841</v>
-      </c>
       <c r="L22" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>882</v>
+        <v>880</v>
       </c>
       <c r="B23" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="C23" t="s">
-        <v>883</v>
+        <v>881</v>
       </c>
       <c r="E23">
         <v>41.812400029925101</v>
@@ -4341,27 +4329,27 @@
         <v>-71.412241566706101</v>
       </c>
       <c r="H23" t="s">
+        <v>837</v>
+      </c>
+      <c r="J23" t="s">
+        <v>882</v>
+      </c>
+      <c r="K23" t="s">
         <v>839</v>
       </c>
-      <c r="J23" t="s">
-        <v>884</v>
-      </c>
-      <c r="K23" t="s">
-        <v>841</v>
-      </c>
       <c r="L23" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="B24" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="C24" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="E24">
         <v>41.815220108104697</v>
@@ -4370,27 +4358,27 @@
         <v>-71.404274370499806</v>
       </c>
       <c r="H24" t="s">
+        <v>837</v>
+      </c>
+      <c r="J24" t="s">
+        <v>885</v>
+      </c>
+      <c r="K24" t="s">
         <v>839</v>
       </c>
-      <c r="J24" t="s">
-        <v>887</v>
-      </c>
-      <c r="K24" t="s">
-        <v>841</v>
-      </c>
       <c r="L24" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
       <c r="B25" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="C25" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
       <c r="E25">
         <v>41.813646314261298</v>
@@ -4399,27 +4387,27 @@
         <v>-71.408648868447401</v>
       </c>
       <c r="H25" t="s">
+        <v>837</v>
+      </c>
+      <c r="J25" t="s">
+        <v>888</v>
+      </c>
+      <c r="K25" t="s">
         <v>839</v>
       </c>
-      <c r="J25" t="s">
-        <v>890</v>
-      </c>
-      <c r="K25" t="s">
-        <v>841</v>
-      </c>
       <c r="L25" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="B26" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="C26" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
       <c r="E26">
         <v>41.809847611086703</v>
@@ -4428,27 +4416,27 @@
         <v>-71.406145309308798</v>
       </c>
       <c r="H26" t="s">
+        <v>837</v>
+      </c>
+      <c r="J26" t="s">
+        <v>891</v>
+      </c>
+      <c r="K26" t="s">
         <v>839</v>
       </c>
-      <c r="J26" t="s">
-        <v>893</v>
-      </c>
-      <c r="K26" t="s">
-        <v>841</v>
-      </c>
       <c r="L26" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="B27" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="C27" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
       <c r="E27">
         <v>41.797595415752703</v>
@@ -4457,27 +4445,27 @@
         <v>-71.393397343566093</v>
       </c>
       <c r="H27" t="s">
+        <v>837</v>
+      </c>
+      <c r="J27" t="s">
+        <v>894</v>
+      </c>
+      <c r="K27" t="s">
         <v>839</v>
       </c>
-      <c r="J27" t="s">
-        <v>896</v>
-      </c>
-      <c r="K27" t="s">
-        <v>841</v>
-      </c>
       <c r="L27" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>897</v>
+        <v>895</v>
       </c>
       <c r="B28" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="C28" t="s">
-        <v>898</v>
+        <v>896</v>
       </c>
       <c r="E28">
         <v>41.818256789472798</v>
@@ -4486,27 +4474,27 @@
         <v>-71.462177468256797</v>
       </c>
       <c r="H28" t="s">
+        <v>837</v>
+      </c>
+      <c r="J28" t="s">
+        <v>897</v>
+      </c>
+      <c r="K28" t="s">
         <v>839</v>
       </c>
-      <c r="J28" t="s">
-        <v>899</v>
-      </c>
-      <c r="K28" t="s">
-        <v>841</v>
-      </c>
       <c r="L28" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>900</v>
+        <v>898</v>
       </c>
       <c r="B29" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="C29" t="s">
-        <v>901</v>
+        <v>899</v>
       </c>
       <c r="E29">
         <v>41.808423769284097</v>
@@ -4515,21 +4503,21 @@
         <v>-71.4041889644311</v>
       </c>
       <c r="H29" t="s">
+        <v>837</v>
+      </c>
+      <c r="J29" t="s">
+        <v>900</v>
+      </c>
+      <c r="K29" t="s">
         <v>839</v>
       </c>
-      <c r="J29" t="s">
-        <v>902</v>
-      </c>
-      <c r="K29" t="s">
-        <v>841</v>
-      </c>
       <c r="L29" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>903</v>
+        <v>901</v>
       </c>
       <c r="B30" t="s">
         <v>81</v>
@@ -4541,18 +4529,18 @@
         <v>-122.3958984850878</v>
       </c>
       <c r="H30" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="K30" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="L30" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>904</v>
+        <v>902</v>
       </c>
       <c r="B31" t="s">
         <v>81</v>
@@ -4564,18 +4552,18 @@
         <v>-122.39123499999999</v>
       </c>
       <c r="H31" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="K31" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="L31" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>905</v>
+        <v>903</v>
       </c>
       <c r="B32" t="s">
         <v>81</v>
@@ -4587,18 +4575,18 @@
         <v>-122.4043954592607</v>
       </c>
       <c r="H32" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="K32" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="L32" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>906</v>
+        <v>904</v>
       </c>
       <c r="B33" t="s">
         <v>81</v>
@@ -4610,18 +4598,18 @@
         <v>-122.3860225810642</v>
       </c>
       <c r="H33" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="K33" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="L33" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>907</v>
+        <v>905</v>
       </c>
       <c r="B34" t="s">
         <v>81</v>
@@ -4633,18 +4621,18 @@
         <v>-122.3845098362131</v>
       </c>
       <c r="H34" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="K34" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="L34" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>908</v>
+        <v>906</v>
       </c>
       <c r="B35" t="s">
         <v>81</v>
@@ -4656,18 +4644,18 @@
         <v>-122.4198403831063</v>
       </c>
       <c r="H35" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="K35" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="L35" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
       <c r="B36" t="s">
         <v>81</v>
@@ -4679,18 +4667,18 @@
         <v>-122.41337432608221</v>
       </c>
       <c r="H36" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="K36" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="L36" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
       <c r="B37" t="s">
         <v>81</v>
@@ -4702,18 +4690,18 @@
         <v>-122.40853351738571</v>
       </c>
       <c r="H37" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="K37" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="L37" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
       <c r="B38" t="s">
         <v>81</v>
@@ -4725,18 +4713,18 @@
         <v>-122.4335677655755</v>
       </c>
       <c r="H38" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="K38" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="L38" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="B39" t="s">
         <v>81</v>
@@ -4748,18 +4736,18 @@
         <v>-122.43744924076159</v>
       </c>
       <c r="H39" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="K39" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="L39" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
       <c r="B40" t="s">
         <v>81</v>
@@ -4771,18 +4759,18 @@
         <v>-122.4355635461724</v>
       </c>
       <c r="H40" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="K40" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="L40" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>914</v>
+        <v>912</v>
       </c>
       <c r="B41" t="s">
         <v>81</v>
@@ -4794,18 +4782,18 @@
         <v>-122.39374288336531</v>
       </c>
       <c r="H41" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="K41" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="L41" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>915</v>
+        <v>913</v>
       </c>
       <c r="B42" t="s">
         <v>81</v>
@@ -4817,18 +4805,18 @@
         <v>-122.3977654783651</v>
       </c>
       <c r="H42" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="K42" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="L42" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>916</v>
+        <v>914</v>
       </c>
       <c r="B43" t="s">
         <v>81</v>
@@ -4840,18 +4828,18 @@
         <v>-122.408067</v>
       </c>
       <c r="H43" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="K43" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="L43" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="B44" t="s">
         <v>213</v>
@@ -4863,18 +4851,18 @@
         <v>-76.611576623679852</v>
       </c>
       <c r="H44" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="K44" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="L44" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="B45" t="s">
         <v>213</v>
@@ -4886,18 +4874,18 @@
         <v>-76.618003662487453</v>
       </c>
       <c r="H45" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="K45" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="L45" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
       <c r="B46" t="s">
         <v>213</v>
@@ -4909,18 +4897,18 @@
         <v>-76.6301632364396</v>
       </c>
       <c r="H46" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="K46" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="L46" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
       <c r="B47" t="s">
         <v>213</v>
@@ -4932,18 +4920,18 @@
         <v>-76.632287528962351</v>
       </c>
       <c r="H47" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="K47" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="L47" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>921</v>
+        <v>919</v>
       </c>
       <c r="B48" t="s">
         <v>213</v>
@@ -4955,18 +4943,18 @@
         <v>-76.610031649710891</v>
       </c>
       <c r="H48" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="K48" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="L48" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="B49" t="s">
         <v>213</v>
@@ -4978,18 +4966,18 @@
         <v>-76.577429543863104</v>
       </c>
       <c r="H49" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="K49" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="L49" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
       <c r="B50" t="s">
         <v>213</v>
@@ -5001,18 +4989,18 @@
         <v>-76.569818011058814</v>
       </c>
       <c r="H50" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="K50" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="L50" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>924</v>
+        <v>922</v>
       </c>
       <c r="B51" t="s">
         <v>213</v>
@@ -5024,18 +5012,18 @@
         <v>-76.620777324652096</v>
       </c>
       <c r="H51" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="K51" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="L51" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="B52" t="s">
         <v>213</v>
@@ -5047,18 +5035,18 @@
         <v>-76.619661757880095</v>
       </c>
       <c r="H52" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="K52" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="L52" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="B53" t="s">
         <v>213</v>
@@ -5070,18 +5058,18 @@
         <v>-76.619432617444204</v>
       </c>
       <c r="H53" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="K53" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="L53" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="B54" t="s">
         <v>213</v>
@@ -5093,18 +5081,18 @@
         <v>-76.563536688426652</v>
       </c>
       <c r="H54" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="K54" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="L54" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
       <c r="B55" t="s">
         <v>351</v>
@@ -5116,18 +5104,18 @@
         <v>-81.704989956945482</v>
       </c>
       <c r="H55" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="K55" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="L55" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="B56" t="s">
         <v>351</v>
@@ -5139,18 +5127,18 @@
         <v>-81.703666050407222</v>
       </c>
       <c r="H56" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="K56" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="L56" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
       <c r="B57" t="s">
         <v>351</v>
@@ -5162,18 +5150,18 @@
         <v>-81.649867780451714</v>
       </c>
       <c r="H57" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="K57" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="L57" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>931</v>
+        <v>929</v>
       </c>
       <c r="B58" t="s">
         <v>351</v>
@@ -5185,18 +5173,18 @@
         <v>-81.71094754852507</v>
       </c>
       <c r="H58" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="K58" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="L58" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>932</v>
+        <v>930</v>
       </c>
       <c r="B59" t="s">
         <v>351</v>
@@ -5208,18 +5196,18 @@
         <v>-81.618602589135307</v>
       </c>
       <c r="H59" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="K59" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="L59" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="B60" t="s">
         <v>351</v>
@@ -5231,18 +5219,18 @@
         <v>-81.674810369449219</v>
       </c>
       <c r="H60" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="K60" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="L60" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>934</v>
+        <v>932</v>
       </c>
       <c r="B61" t="s">
         <v>351</v>
@@ -5254,18 +5242,18 @@
         <v>-81.772018382180718</v>
       </c>
       <c r="H61" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="K61" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="L61" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>935</v>
+        <v>933</v>
       </c>
       <c r="B62" t="s">
         <v>351</v>
@@ -5277,24 +5265,24 @@
         <v>-81.655506254139397</v>
       </c>
       <c r="H62" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="K62" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="L62" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>936</v>
+        <v>934</v>
       </c>
       <c r="B63" t="s">
         <v>320</v>
       </c>
       <c r="C63" t="s">
-        <v>937</v>
+        <v>935</v>
       </c>
       <c r="E63">
         <v>39.083004536451213</v>
@@ -5303,27 +5291,27 @@
         <v>-94.605364115903598</v>
       </c>
       <c r="H63" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="J63" t="s">
-        <v>938</v>
+        <v>936</v>
       </c>
       <c r="K63" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="L63" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>939</v>
+        <v>937</v>
       </c>
       <c r="B64" t="s">
         <v>320</v>
       </c>
       <c r="C64" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
       <c r="E64">
         <v>39.113579705315239</v>
@@ -5332,27 +5320,27 @@
         <v>-94.573468210035685</v>
       </c>
       <c r="H64" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="J64" t="s">
-        <v>941</v>
+        <v>939</v>
       </c>
       <c r="K64" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="L64" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>942</v>
+        <v>940</v>
       </c>
       <c r="B65" t="s">
         <v>320</v>
       </c>
       <c r="C65" t="s">
-        <v>943</v>
+        <v>941</v>
       </c>
       <c r="E65">
         <v>39.113050970862901</v>
@@ -5361,27 +5349,27 @@
         <v>-94.570777106104174</v>
       </c>
       <c r="H65" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="J65" t="s">
-        <v>944</v>
+        <v>942</v>
       </c>
       <c r="K65" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="L65" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>945</v>
+        <v>943</v>
       </c>
       <c r="B66" t="s">
         <v>320</v>
       </c>
       <c r="C66" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
       <c r="E66">
         <v>39.086666551279848</v>
@@ -5390,27 +5378,27 @@
         <v>-94.593375605896483</v>
       </c>
       <c r="H66" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="J66" t="s">
-        <v>947</v>
+        <v>945</v>
       </c>
       <c r="K66" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="L66" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>948</v>
+        <v>946</v>
       </c>
       <c r="B67" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C67" t="s">
-        <v>949</v>
+        <v>947</v>
       </c>
       <c r="E67">
         <v>41.913641473620729</v>
@@ -5419,27 +5407,27 @@
         <v>-87.655915933688348</v>
       </c>
       <c r="H67" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="J67" t="s">
-        <v>950</v>
+        <v>948</v>
       </c>
       <c r="K67" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="L67" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="B68" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C68" t="s">
-        <v>952</v>
+        <v>950</v>
       </c>
       <c r="E68">
         <v>41.912577676609779</v>
@@ -5448,27 +5436,27 @@
         <v>-87.656497859388253</v>
       </c>
       <c r="H68" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="J68" t="s">
-        <v>953</v>
+        <v>951</v>
       </c>
       <c r="K68" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="L68" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>954</v>
+        <v>952</v>
       </c>
       <c r="B69" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C69" t="s">
-        <v>955</v>
+        <v>953</v>
       </c>
       <c r="E69">
         <v>41.902301702333091</v>
@@ -5477,24 +5465,24 @@
         <v>-87.646311777501381</v>
       </c>
       <c r="H69" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="J69" t="s">
-        <v>956</v>
+        <v>954</v>
       </c>
       <c r="K69" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="L69" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>957</v>
+        <v>955</v>
       </c>
       <c r="B70" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="E70">
         <v>41.847770156543369</v>
@@ -5503,24 +5491,24 @@
         <v>-87.639314085854835</v>
       </c>
       <c r="H70" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="J70" t="s">
-        <v>958</v>
+        <v>956</v>
       </c>
       <c r="K70" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="L70" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>959</v>
+        <v>957</v>
       </c>
       <c r="B71" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="E71">
         <v>41.844190422812531</v>
@@ -5529,24 +5517,24 @@
         <v>-87.66212860575007</v>
       </c>
       <c r="H71" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="J71" t="s">
-        <v>960</v>
+        <v>958</v>
       </c>
       <c r="K71" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="L71" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>961</v>
+        <v>959</v>
       </c>
       <c r="B72" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="E72">
         <v>41.847564252160922</v>
@@ -5555,24 +5543,24 @@
         <v>-87.649901873871485</v>
       </c>
       <c r="H72" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="J72" t="s">
-        <v>962</v>
+        <v>960</v>
       </c>
       <c r="K72" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="L72" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>963</v>
+        <v>961</v>
       </c>
       <c r="B73" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="E73">
         <v>41.845160763375119</v>
@@ -5581,27 +5569,27 @@
         <v>-87.64936620743832</v>
       </c>
       <c r="H73" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="J73" t="s">
-        <v>964</v>
+        <v>962</v>
       </c>
       <c r="K73" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="L73" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>965</v>
+        <v>963</v>
       </c>
       <c r="B74" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C74" t="s">
-        <v>966</v>
+        <v>964</v>
       </c>
       <c r="E74">
         <v>41.837672021485609</v>
@@ -5610,27 +5598,27 @@
         <v>-87.662619816527297</v>
       </c>
       <c r="H74" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="J74" t="s">
-        <v>967</v>
+        <v>965</v>
       </c>
       <c r="K74" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="L74" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>968</v>
+        <v>966</v>
       </c>
       <c r="B75" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C75" t="s">
-        <v>969</v>
+        <v>967</v>
       </c>
       <c r="E75">
         <v>41.837278184098473</v>
@@ -5639,24 +5627,24 @@
         <v>-87.662009072757598</v>
       </c>
       <c r="H75" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="J75" t="s">
-        <v>970</v>
+        <v>968</v>
       </c>
       <c r="K75" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="L75" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>971</v>
+        <v>969</v>
       </c>
       <c r="B76" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="E76">
         <v>41.837241383809058</v>
@@ -5665,27 +5653,27 @@
         <v>-87.647393936651014</v>
       </c>
       <c r="H76" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="J76" t="s">
-        <v>972</v>
+        <v>970</v>
       </c>
       <c r="K76" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="L76" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>973</v>
+        <v>971</v>
       </c>
       <c r="B77" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C77" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
       <c r="E77">
         <v>41.901574093038498</v>
@@ -5694,27 +5682,27 @@
         <v>-87.658375297222136</v>
       </c>
       <c r="H77" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="J77" t="s">
-        <v>975</v>
+        <v>973</v>
       </c>
       <c r="K77" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="L77" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>976</v>
+        <v>974</v>
       </c>
       <c r="B78" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C78" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
       <c r="E78">
         <v>41.903045015519417</v>
@@ -5723,27 +5711,27 @@
         <v>-87.659286870241928</v>
       </c>
       <c r="H78" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="J78" t="s">
-        <v>977</v>
+        <v>975</v>
       </c>
       <c r="K78" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="L78" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>978</v>
+        <v>976</v>
       </c>
       <c r="B79" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C79" t="s">
-        <v>979</v>
+        <v>977</v>
       </c>
       <c r="E79">
         <v>41.859315020296123</v>
@@ -5752,27 +5740,27 @@
         <v>-87.641343011982698</v>
       </c>
       <c r="H79" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="J79" t="s">
-        <v>980</v>
+        <v>978</v>
       </c>
       <c r="K79" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="L79" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
       <c r="B80" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C80" t="s">
-        <v>982</v>
+        <v>980</v>
       </c>
       <c r="E80">
         <v>41.850817677456568</v>
@@ -5781,27 +5769,27 @@
         <v>-87.656931660907546</v>
       </c>
       <c r="H80" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="J80" t="s">
-        <v>983</v>
+        <v>981</v>
       </c>
       <c r="K80" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="L80" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>984</v>
+        <v>982</v>
       </c>
       <c r="B81" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C81" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
       <c r="E81">
         <v>41.84964157682456</v>
@@ -5810,27 +5798,27 @@
         <v>-87.65699541488766</v>
       </c>
       <c r="H81" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="J81" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="K81" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="L81" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>987</v>
+        <v>985</v>
       </c>
       <c r="B82" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C82" t="s">
-        <v>988</v>
+        <v>986</v>
       </c>
       <c r="E82">
         <v>41.848990061514648</v>
@@ -5839,24 +5827,24 @@
         <v>-87.655641532140578</v>
       </c>
       <c r="H82" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="J82" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="K82" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="L82" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>990</v>
+        <v>988</v>
       </c>
       <c r="B83" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="E83">
         <v>41.861242283603033</v>
@@ -5865,27 +5853,27 @@
         <v>-87.74270832412185</v>
       </c>
       <c r="H83" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="J83" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="K83" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="L83" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
     </row>
     <row r="84" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="B84" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C84" t="s">
-        <v>993</v>
+        <v>991</v>
       </c>
       <c r="E84">
         <v>41.846508394129202</v>
@@ -5894,24 +5882,24 @@
         <v>-87.74190199522117</v>
       </c>
       <c r="H84" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="J84" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="K84" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="L84" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="B85" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="E85">
         <v>41.692228192254589</v>
@@ -5920,30 +5908,30 @@
         <v>-87.547014248314227</v>
       </c>
       <c r="H85" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="J85" t="s">
-        <v>996</v>
+        <v>994</v>
       </c>
       <c r="K85" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="L85" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
+        <v>995</v>
+      </c>
+      <c r="B86" t="s">
+        <v>451</v>
+      </c>
+      <c r="C86" t="s">
+        <v>996</v>
+      </c>
+      <c r="D86" t="s">
         <v>997</v>
-      </c>
-      <c r="B86" t="s">
-        <v>453</v>
-      </c>
-      <c r="C86" t="s">
-        <v>998</v>
-      </c>
-      <c r="D86" t="s">
-        <v>999</v>
       </c>
       <c r="E86">
         <v>41.683796205888498</v>
@@ -5952,27 +5940,27 @@
         <v>-87.542631386912305</v>
       </c>
       <c r="H86" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="J86" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
       <c r="K86" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="L86" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
     </row>
     <row r="87" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="B87" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="D87" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
       <c r="E87">
         <v>41.707304325158972</v>
@@ -5981,27 +5969,27 @@
         <v>-87.559003419465498</v>
       </c>
       <c r="H87" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="J87" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="K87" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="L87" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>1004</v>
+        <v>1002</v>
       </c>
       <c r="B88" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C88" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="E88">
         <v>41.890210521695117</v>
@@ -6010,27 +5998,27 @@
         <v>-87.695443899775981</v>
       </c>
       <c r="H88" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="J88" t="s">
-        <v>1006</v>
+        <v>1004</v>
       </c>
       <c r="K88" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="L88" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
     </row>
     <row r="89" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="B89" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="D89" t="s">
-        <v>1008</v>
+        <v>1006</v>
       </c>
       <c r="E89">
         <v>41.721397743833762</v>
@@ -6039,27 +6027,27 @@
         <v>-87.547783248630793</v>
       </c>
       <c r="H89" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="J89" t="s">
-        <v>1009</v>
+        <v>1007</v>
       </c>
       <c r="K89" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="L89" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="B90" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C90" t="s">
-        <v>1011</v>
+        <v>1009</v>
       </c>
       <c r="E90">
         <v>41.693674236045553</v>
@@ -6068,27 +6056,27 @@
         <v>-87.603408419812112</v>
       </c>
       <c r="H90" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="J90" t="s">
-        <v>1012</v>
+        <v>1010</v>
       </c>
       <c r="K90" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="L90" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
     </row>
     <row r="91" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
       <c r="B91" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C91" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="E91">
         <v>41.761209532894362</v>
@@ -6097,27 +6085,27 @@
         <v>-87.600198638837881</v>
       </c>
       <c r="H91" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="J91" t="s">
-        <v>1015</v>
+        <v>1013</v>
       </c>
       <c r="K91" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="L91" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
     </row>
     <row r="92" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
       <c r="B92" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C92" t="s">
-        <v>1017</v>
+        <v>1015</v>
       </c>
       <c r="E92">
         <v>42.024724154327671</v>
@@ -6126,27 +6114,27 @@
         <v>-87.712859541256563</v>
       </c>
       <c r="H92" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="J92" t="s">
-        <v>1018</v>
+        <v>1016</v>
       </c>
       <c r="K92" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="L92" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
     </row>
     <row r="93" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="B93" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C93" t="s">
-        <v>1020</v>
+        <v>1018</v>
       </c>
       <c r="E93">
         <v>41.689779349147067</v>
@@ -6155,27 +6143,27 @@
         <v>-87.548662824135221</v>
       </c>
       <c r="H93" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="J93" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="K93" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="L93" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
     </row>
     <row r="94" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
       <c r="B94" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C94" t="s">
-        <v>1023</v>
+        <v>1021</v>
       </c>
       <c r="E94">
         <v>41.694092794141199</v>
@@ -6184,27 +6172,27 @@
         <v>-87.560703641659416</v>
       </c>
       <c r="H94" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="J94" t="s">
-        <v>1024</v>
+        <v>1022</v>
       </c>
       <c r="K94" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="L94" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
       <c r="B95" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C95" t="s">
-        <v>1026</v>
+        <v>1024</v>
       </c>
       <c r="E95">
         <v>41.695461963593623</v>
@@ -6213,30 +6201,30 @@
         <v>-87.557314418031993</v>
       </c>
       <c r="H95" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="J95" t="s">
-        <v>1027</v>
+        <v>1025</v>
       </c>
       <c r="K95" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="L95" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
     </row>
     <row r="96" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
+        <v>1026</v>
+      </c>
+      <c r="B96" t="s">
+        <v>451</v>
+      </c>
+      <c r="C96" t="s">
+        <v>1027</v>
+      </c>
+      <c r="D96" t="s">
         <v>1028</v>
-      </c>
-      <c r="B96" t="s">
-        <v>453</v>
-      </c>
-      <c r="C96" t="s">
-        <v>1029</v>
-      </c>
-      <c r="D96" t="s">
-        <v>1030</v>
       </c>
       <c r="E96">
         <v>41.718309701015563</v>
@@ -6245,27 +6233,27 @@
         <v>-87.546017735887091</v>
       </c>
       <c r="H96" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="J96" t="s">
-        <v>1031</v>
+        <v>1029</v>
       </c>
       <c r="K96" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="L96" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
     </row>
     <row r="97" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>1032</v>
+        <v>1030</v>
       </c>
       <c r="B97" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C97" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
       <c r="E97">
         <v>41.728699894289257</v>
@@ -6274,27 +6262,27 @@
         <v>-87.541630978260173</v>
       </c>
       <c r="H97" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="J97" t="s">
-        <v>1034</v>
+        <v>1032</v>
       </c>
       <c r="K97" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="L97" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
     </row>
     <row r="98" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A98" s="3" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="E98" s="3">
         <v>41.828497084750801</v>
@@ -6303,27 +6291,27 @@
         <v>-87.732864664578301</v>
       </c>
       <c r="H98" s="3" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="J98" s="3" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
       <c r="K98" s="3" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="L98" s="3" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
     </row>
     <row r="99" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A99" s="3" t="s">
-        <v>1038</v>
+        <v>1036</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>1039</v>
+        <v>1037</v>
       </c>
       <c r="E99" s="3">
         <v>41.828653670634083</v>
@@ -6332,24 +6320,24 @@
         <v>-87.726131183128274</v>
       </c>
       <c r="H99" s="3" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="J99" s="3" t="s">
-        <v>1040</v>
+        <v>1038</v>
       </c>
       <c r="K99" s="3" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="L99" s="3" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
     </row>
     <row r="100" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>1041</v>
+        <v>1039</v>
       </c>
       <c r="B100" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="E100">
         <v>41.651482871851449</v>
@@ -6358,24 +6346,24 @@
         <v>-87.685581287686091</v>
       </c>
       <c r="H100" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="J100" t="s">
-        <v>1042</v>
+        <v>1040</v>
       </c>
       <c r="K100" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="L100" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
       <c r="B101" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="E101">
         <v>41.870580057360918</v>
@@ -6384,24 +6372,24 @@
         <v>-87.77898712406764</v>
       </c>
       <c r="H101" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="J101" t="s">
-        <v>1044</v>
+        <v>1042</v>
       </c>
       <c r="K101" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="L101" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
     </row>
     <row r="102" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>1045</v>
+        <v>1043</v>
       </c>
       <c r="B102" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="E102">
         <v>41.501350271031967</v>
@@ -6410,24 +6398,24 @@
         <v>-87.617978407874503</v>
       </c>
       <c r="H102" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="J102" t="s">
-        <v>1046</v>
+        <v>1044</v>
       </c>
       <c r="K102" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="L102" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
     </row>
     <row r="103" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>1047</v>
+        <v>1045</v>
       </c>
       <c r="B103" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="E103">
         <v>41.805620164580169</v>
@@ -6436,24 +6424,24 @@
         <v>-87.861021388103964</v>
       </c>
       <c r="H103" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="J103" t="s">
-        <v>1048</v>
+        <v>1046</v>
       </c>
       <c r="K103" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="L103" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
     </row>
     <row r="104" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>1049</v>
+        <v>1047</v>
       </c>
       <c r="B104" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="E104">
         <v>41.695018391199348</v>
@@ -6462,27 +6450,27 @@
         <v>-87.560328594451661</v>
       </c>
       <c r="H104" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="J104" t="s">
-        <v>1050</v>
+        <v>1048</v>
       </c>
       <c r="K104" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="L104" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
     </row>
     <row r="105" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>1051</v>
+        <v>1049</v>
       </c>
       <c r="B105" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="C105" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
       <c r="E105">
         <v>41.887019332256912</v>
@@ -6491,27 +6479,27 @@
         <v>-71.384772194712482</v>
       </c>
       <c r="H105" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="J105" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="K105" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="L105" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
     </row>
     <row r="106" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="B106" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="C106" t="s">
-        <v>1055</v>
+        <v>1053</v>
       </c>
       <c r="E106">
         <v>41.869142269010048</v>
@@ -6520,27 +6508,27 @@
         <v>-71.38287057006977</v>
       </c>
       <c r="H106" t="s">
+        <v>837</v>
+      </c>
+      <c r="J106" t="s">
+        <v>1051</v>
+      </c>
+      <c r="K106" t="s">
         <v>839</v>
       </c>
-      <c r="J106" t="s">
-        <v>1053</v>
-      </c>
-      <c r="K106" t="s">
-        <v>841</v>
-      </c>
       <c r="L106" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
     </row>
     <row r="107" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>1056</v>
+        <v>1054</v>
       </c>
       <c r="B107" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="C107" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="E107">
         <v>41.879358776161901</v>
@@ -6549,27 +6537,27 @@
         <v>-71.382880126864052</v>
       </c>
       <c r="H107" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="J107" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="K107" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="L107" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
     </row>
     <row r="108" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="B108" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="C108" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="E108">
         <v>41.838498493550873</v>
@@ -6578,27 +6566,27 @@
         <v>-71.352849643292814</v>
       </c>
       <c r="H108" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="J108" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="K108" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="L108" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
     </row>
     <row r="109" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>1060</v>
+        <v>1058</v>
       </c>
       <c r="B109" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="C109" t="s">
-        <v>1061</v>
+        <v>1059</v>
       </c>
       <c r="E109">
         <v>41.816318917311037</v>
@@ -6607,27 +6595,27 @@
         <v>-71.385456659271696</v>
       </c>
       <c r="H109" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="J109" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="K109" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="L109" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
     </row>
     <row r="110" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>1062</v>
+        <v>1060</v>
       </c>
       <c r="B110" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="C110" t="s">
-        <v>1063</v>
+        <v>1061</v>
       </c>
       <c r="E110">
         <v>41.842019572538831</v>
@@ -6636,27 +6624,27 @@
         <v>-71.409501546617761</v>
       </c>
       <c r="H110" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="J110" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="K110" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="L110" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
     </row>
     <row r="111" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>1065</v>
+        <v>1063</v>
       </c>
       <c r="B111" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="C111" t="s">
-        <v>1066</v>
+        <v>1064</v>
       </c>
       <c r="E111">
         <v>41.845446802960772</v>
@@ -6665,27 +6653,27 @@
         <v>-71.36966810028872</v>
       </c>
       <c r="H111" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="J111" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="K111" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="L111" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
     </row>
     <row r="112" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="B112" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="C112" t="s">
-        <v>1068</v>
+        <v>1066</v>
       </c>
       <c r="E112">
         <v>47.599628840825631</v>
@@ -6694,27 +6682,27 @@
         <v>-122.32832893580721</v>
       </c>
       <c r="H112" t="s">
+        <v>837</v>
+      </c>
+      <c r="J112" t="s">
+        <v>1067</v>
+      </c>
+      <c r="K112" t="s">
         <v>839</v>
       </c>
-      <c r="J112" t="s">
-        <v>1069</v>
-      </c>
-      <c r="K112" t="s">
-        <v>841</v>
-      </c>
       <c r="L112" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
     </row>
     <row r="113" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>1070</v>
+        <v>1068</v>
       </c>
       <c r="B113" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="C113" t="s">
-        <v>1071</v>
+        <v>1069</v>
       </c>
       <c r="E113">
         <v>47.629013757404849</v>
@@ -6723,27 +6711,27 @@
         <v>-122.37268219282529</v>
       </c>
       <c r="H113" t="s">
+        <v>837</v>
+      </c>
+      <c r="J113" t="s">
+        <v>1067</v>
+      </c>
+      <c r="K113" t="s">
         <v>839</v>
       </c>
-      <c r="J113" t="s">
-        <v>1069</v>
-      </c>
-      <c r="K113" t="s">
-        <v>841</v>
-      </c>
       <c r="L113" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
     </row>
     <row r="114" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>1072</v>
+        <v>1070</v>
       </c>
       <c r="B114" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="C114" t="s">
-        <v>1073</v>
+        <v>1071</v>
       </c>
       <c r="E114">
         <v>47.623854771795649</v>
@@ -6752,27 +6740,27 @@
         <v>-122.34041756226119</v>
       </c>
       <c r="H114" t="s">
+        <v>837</v>
+      </c>
+      <c r="J114" t="s">
+        <v>1067</v>
+      </c>
+      <c r="K114" t="s">
         <v>839</v>
       </c>
-      <c r="J114" t="s">
-        <v>1069</v>
-      </c>
-      <c r="K114" t="s">
-        <v>841</v>
-      </c>
       <c r="L114" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
     </row>
     <row r="115" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>1074</v>
+        <v>1072</v>
       </c>
       <c r="B115" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="C115" t="s">
-        <v>1075</v>
+        <v>1073</v>
       </c>
       <c r="E115">
         <v>47.64594084767392</v>
@@ -6781,16 +6769,16 @@
         <v>-122.33384530382141</v>
       </c>
       <c r="H115" t="s">
+        <v>837</v>
+      </c>
+      <c r="J115" t="s">
+        <v>1067</v>
+      </c>
+      <c r="K115" t="s">
         <v>839</v>
       </c>
-      <c r="J115" t="s">
-        <v>1069</v>
-      </c>
-      <c r="K115" t="s">
-        <v>841</v>
-      </c>
       <c r="L115" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
     </row>
   </sheetData>
@@ -6800,7 +6788,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:I266"/>
+  <dimension ref="A1:I265"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
@@ -7629,6 +7617,9 @@
       <c r="E37" t="s">
         <v>122</v>
       </c>
+      <c r="F37" t="s">
+        <v>138</v>
+      </c>
       <c r="H37" t="s">
         <v>14</v>
       </c>
@@ -9716,7 +9707,7 @@
     </row>
     <row r="135" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B135" t="s">
         <v>81</v>
@@ -9725,10 +9716,13 @@
         <v>1950</v>
       </c>
       <c r="D135" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="E135" t="s">
-        <v>421</v>
+        <v>422</v>
+      </c>
+      <c r="F135" t="s">
+        <v>138</v>
       </c>
       <c r="H135" t="s">
         <v>14</v>
@@ -9736,27 +9730,30 @@
     </row>
     <row r="136" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B136" t="s">
         <v>81</v>
       </c>
       <c r="C136">
-        <v>1950</v>
+        <v>1893</v>
       </c>
       <c r="D136" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="E136" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H136" t="s">
         <v>14</v>
+      </c>
+      <c r="I136" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="137" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B137" t="s">
         <v>81</v>
@@ -9765,33 +9762,33 @@
         <v>1893</v>
       </c>
       <c r="D137" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="E137" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H137" t="s">
         <v>14</v>
       </c>
       <c r="I137" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="138" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B138" t="s">
         <v>81</v>
       </c>
       <c r="C138">
-        <v>1893</v>
+        <v>1889</v>
       </c>
       <c r="D138" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E138" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H138" t="s">
         <v>14</v>
@@ -9802,30 +9799,27 @@
     </row>
     <row r="139" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B139" t="s">
-        <v>81</v>
+        <v>351</v>
       </c>
       <c r="C139">
-        <v>1889</v>
+        <v>1886</v>
       </c>
       <c r="D139" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="E139" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H139" t="s">
         <v>14</v>
-      </c>
-      <c r="I139" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="140" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B140" t="s">
         <v>351</v>
@@ -9834,10 +9828,10 @@
         <v>1886</v>
       </c>
       <c r="D140" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="E140" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H140" t="s">
         <v>14</v>
@@ -9845,19 +9839,19 @@
     </row>
     <row r="141" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B141" t="s">
         <v>351</v>
       </c>
       <c r="C141">
-        <v>1886</v>
+        <v>1896</v>
       </c>
       <c r="D141" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="E141" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H141" t="s">
         <v>14</v>
@@ -9865,19 +9859,19 @@
     </row>
     <row r="142" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B142" t="s">
         <v>351</v>
       </c>
       <c r="C142">
-        <v>1896</v>
+        <v>1886</v>
       </c>
       <c r="D142" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="E142" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="H142" t="s">
         <v>14</v>
@@ -9885,27 +9879,30 @@
     </row>
     <row r="143" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B143" t="s">
         <v>351</v>
       </c>
       <c r="C143">
-        <v>1886</v>
+        <v>1887</v>
       </c>
       <c r="D143" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="E143" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H143" t="s">
         <v>14</v>
+      </c>
+      <c r="I143" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="144" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B144" t="s">
         <v>351</v>
@@ -9914,339 +9911,336 @@
         <v>1887</v>
       </c>
       <c r="D144" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="E144" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H144" t="s">
         <v>14</v>
       </c>
       <c r="I144" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="145" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B145" t="s">
-        <v>351</v>
+        <v>451</v>
       </c>
       <c r="C145">
-        <v>1887</v>
+        <v>1910</v>
       </c>
       <c r="D145" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="E145" t="s">
+        <v>453</v>
+      </c>
+      <c r="H145" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="146" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>454</v>
+      </c>
+      <c r="B146" t="s">
         <v>451</v>
       </c>
-      <c r="H145" t="s">
-        <v>14</v>
-      </c>
-      <c r="I145" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="146" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A146" t="s">
-        <v>452</v>
-      </c>
-      <c r="B146" t="s">
-        <v>453</v>
-      </c>
       <c r="C146">
+        <v>1950</v>
+      </c>
+      <c r="D146" t="s">
+        <v>455</v>
+      </c>
+      <c r="E146" t="s">
+        <v>456</v>
+      </c>
+      <c r="H146" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="147" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>457</v>
+      </c>
+      <c r="B147" t="s">
+        <v>451</v>
+      </c>
+      <c r="C147">
         <v>1910</v>
       </c>
-      <c r="D146" t="s">
-        <v>454</v>
-      </c>
-      <c r="E146" t="s">
-        <v>455</v>
-      </c>
-      <c r="H146" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A147" t="s">
-        <v>456</v>
-      </c>
-      <c r="B147" t="s">
-        <v>453</v>
-      </c>
-      <c r="C147">
-        <v>1950</v>
-      </c>
       <c r="D147" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="E147" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H147" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B148" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C148">
         <v>1910</v>
       </c>
       <c r="D148" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="E148" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H148" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="149" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B149" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C149">
-        <v>1910</v>
+        <v>1950</v>
       </c>
       <c r="D149" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="E149" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H149" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B150" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C150">
-        <v>1950</v>
+        <v>1911</v>
       </c>
       <c r="D150" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="E150" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H150" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="151" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B151" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C151">
         <v>1911</v>
       </c>
       <c r="D151" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="E151" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H151" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="152" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B152" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C152">
+        <v>1950</v>
+      </c>
+      <c r="D152" t="s">
+        <v>473</v>
+      </c>
+      <c r="E152" t="s">
+        <v>474</v>
+      </c>
+      <c r="H152" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="153" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
+        <v>475</v>
+      </c>
+      <c r="B153" t="s">
+        <v>451</v>
+      </c>
+      <c r="C153">
         <v>1911</v>
       </c>
-      <c r="D152" t="s">
-        <v>472</v>
-      </c>
-      <c r="E152" t="s">
-        <v>473</v>
-      </c>
-      <c r="H152" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="153" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A153" t="s">
-        <v>474</v>
-      </c>
-      <c r="B153" t="s">
-        <v>453</v>
-      </c>
-      <c r="C153">
-        <v>1950</v>
-      </c>
       <c r="D153" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="E153" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H153" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B154" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C154">
         <v>1911</v>
       </c>
       <c r="D154" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="E154" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H154" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="155" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B155" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C155">
         <v>1911</v>
       </c>
       <c r="D155" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="E155" t="s">
-        <v>482</v>
+        <v>483</v>
+      </c>
+      <c r="F155" t="s">
+        <v>138</v>
       </c>
       <c r="H155" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="156" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B156" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C156">
-        <v>1911</v>
+        <v>1912</v>
       </c>
       <c r="D156" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="E156" t="s">
-        <v>485</v>
-      </c>
-      <c r="F156" t="s">
-        <v>138</v>
+        <v>486</v>
       </c>
       <c r="H156" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="157" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B157" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C157">
         <v>1912</v>
       </c>
       <c r="D157" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="E157" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="H157" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="158" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B158" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C158">
-        <v>1912</v>
+        <v>1914</v>
       </c>
       <c r="D158" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="E158" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H158" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="159" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B159" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C159">
+        <v>1950</v>
+      </c>
+      <c r="D159" t="s">
+        <v>494</v>
+      </c>
+      <c r="E159" t="s">
+        <v>495</v>
+      </c>
+      <c r="H159" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="160" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A160" t="s">
+        <v>496</v>
+      </c>
+      <c r="B160" t="s">
+        <v>451</v>
+      </c>
+      <c r="C160">
         <v>1914</v>
       </c>
-      <c r="D159" t="s">
-        <v>493</v>
-      </c>
-      <c r="E159" t="s">
-        <v>494</v>
-      </c>
-      <c r="H159" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="160" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A160" t="s">
-        <v>495</v>
-      </c>
-      <c r="B160" t="s">
-        <v>453</v>
-      </c>
-      <c r="C160">
-        <v>1950</v>
-      </c>
       <c r="D160" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="E160" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H160" t="s">
         <v>14</v>
@@ -10254,19 +10248,19 @@
     </row>
     <row r="161" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B161" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C161">
-        <v>1914</v>
+        <v>1950</v>
       </c>
       <c r="D161" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="E161" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H161" t="s">
         <v>14</v>
@@ -10274,19 +10268,19 @@
     </row>
     <row r="162" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B162" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C162">
-        <v>1950</v>
+        <v>1914</v>
       </c>
       <c r="D162" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="E162" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H162" t="s">
         <v>14</v>
@@ -10294,19 +10288,19 @@
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B163" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C163">
         <v>1914</v>
       </c>
       <c r="D163" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="E163" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H163" t="s">
         <v>14</v>
@@ -10314,19 +10308,19 @@
     </row>
     <row r="164" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B164" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C164">
-        <v>1914</v>
+        <v>1950</v>
       </c>
       <c r="D164" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="E164" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H164" t="s">
         <v>14</v>
@@ -10334,19 +10328,19 @@
     </row>
     <row r="165" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B165" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C165">
-        <v>1950</v>
+        <v>1914</v>
       </c>
       <c r="D165" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="E165" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="H165" t="s">
         <v>14</v>
@@ -10354,19 +10348,19 @@
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B166" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C166">
-        <v>1914</v>
+        <v>1950</v>
       </c>
       <c r="D166" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="E166" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H166" t="s">
         <v>14</v>
@@ -10374,19 +10368,22 @@
     </row>
     <row r="167" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B167" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C167">
         <v>1950</v>
       </c>
       <c r="D167" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="E167" t="s">
-        <v>518</v>
+        <v>519</v>
+      </c>
+      <c r="F167" t="s">
+        <v>138</v>
       </c>
       <c r="H167" t="s">
         <v>14</v>
@@ -10394,22 +10391,19 @@
     </row>
     <row r="168" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B168" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C168">
-        <v>1950</v>
+        <v>1918</v>
       </c>
       <c r="D168" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="E168" t="s">
-        <v>521</v>
-      </c>
-      <c r="F168" t="s">
-        <v>138</v>
+        <v>522</v>
       </c>
       <c r="H168" t="s">
         <v>14</v>
@@ -10417,19 +10411,19 @@
     </row>
     <row r="169" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B169" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C169">
-        <v>1918</v>
+        <v>1950</v>
       </c>
       <c r="D169" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="E169" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="H169" t="s">
         <v>14</v>
@@ -10437,19 +10431,19 @@
     </row>
     <row r="170" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B170" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C170">
-        <v>1950</v>
+        <v>1918</v>
       </c>
       <c r="D170" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="E170" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H170" t="s">
         <v>14</v>
@@ -10457,19 +10451,19 @@
     </row>
     <row r="171" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B171" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C171">
-        <v>1918</v>
+        <v>1909</v>
       </c>
       <c r="D171" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="E171" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H171" t="s">
         <v>14</v>
@@ -10477,19 +10471,19 @@
     </row>
     <row r="172" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B172" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C172">
-        <v>1909</v>
+        <v>1919</v>
       </c>
       <c r="D172" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="E172" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H172" t="s">
         <v>14</v>
@@ -10497,19 +10491,19 @@
     </row>
     <row r="173" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B173" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C173">
-        <v>1919</v>
+        <v>1946</v>
       </c>
       <c r="D173" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="E173" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H173" t="s">
         <v>14</v>
@@ -10517,19 +10511,19 @@
     </row>
     <row r="174" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B174" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C174">
         <v>1946</v>
       </c>
       <c r="D174" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="E174" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="H174" t="s">
         <v>14</v>
@@ -10537,19 +10531,19 @@
     </row>
     <row r="175" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B175" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C175">
         <v>1946</v>
       </c>
       <c r="D175" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="E175" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H175" t="s">
         <v>14</v>
@@ -10557,19 +10551,19 @@
     </row>
     <row r="176" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B176" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C176">
-        <v>1946</v>
+        <v>1911</v>
       </c>
       <c r="D176" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="E176" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H176" t="s">
         <v>14</v>
@@ -10577,19 +10571,19 @@
     </row>
     <row r="177" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B177" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C177">
         <v>1911</v>
       </c>
       <c r="D177" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="E177" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="H177" t="s">
         <v>14</v>
@@ -10597,19 +10591,19 @@
     </row>
     <row r="178" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B178" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C178">
-        <v>1911</v>
+        <v>1909</v>
       </c>
       <c r="D178" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="E178" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="H178" t="s">
         <v>14</v>
@@ -10617,19 +10611,19 @@
     </row>
     <row r="179" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B179" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C179">
-        <v>1909</v>
+        <v>1913</v>
       </c>
       <c r="D179" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="E179" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="H179" t="s">
         <v>14</v>
@@ -10637,19 +10631,19 @@
     </row>
     <row r="180" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B180" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C180">
-        <v>1913</v>
+        <v>1946</v>
       </c>
       <c r="D180" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="E180" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="H180" t="s">
         <v>14</v>
@@ -10657,19 +10651,19 @@
     </row>
     <row r="181" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B181" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C181">
-        <v>1946</v>
+        <v>1935</v>
       </c>
       <c r="D181" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="E181" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="H181" t="s">
         <v>14</v>
@@ -10677,19 +10671,19 @@
     </row>
     <row r="182" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B182" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C182">
         <v>1935</v>
       </c>
       <c r="D182" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="E182" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="H182" t="s">
         <v>14</v>
@@ -10697,19 +10691,19 @@
     </row>
     <row r="183" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B183" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C183">
-        <v>1935</v>
+        <v>1950</v>
       </c>
       <c r="D183" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="E183" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="H183" t="s">
         <v>14</v>
@@ -10717,19 +10711,22 @@
     </row>
     <row r="184" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B184" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C184">
-        <v>1950</v>
+        <v>1936</v>
       </c>
       <c r="D184" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="E184" t="s">
-        <v>569</v>
+        <v>570</v>
+      </c>
+      <c r="F184" t="s">
+        <v>138</v>
       </c>
       <c r="H184" t="s">
         <v>14</v>
@@ -10737,19 +10734,19 @@
     </row>
     <row r="185" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B185" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C185">
         <v>1936</v>
       </c>
       <c r="D185" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="E185" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="F185" t="s">
         <v>138</v>
@@ -10760,19 +10757,19 @@
     </row>
     <row r="186" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B186" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C186">
-        <v>1936</v>
+        <v>1951</v>
       </c>
       <c r="D186" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="E186" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="F186" t="s">
         <v>138</v>
@@ -10783,19 +10780,19 @@
     </row>
     <row r="187" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B187" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C187">
         <v>1951</v>
       </c>
       <c r="D187" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="E187" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="F187" t="s">
         <v>138</v>
@@ -10806,22 +10803,19 @@
     </row>
     <row r="188" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B188" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C188">
-        <v>1951</v>
+        <v>1947</v>
       </c>
       <c r="D188" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="E188" t="s">
-        <v>581</v>
-      </c>
-      <c r="F188" t="s">
-        <v>138</v>
+        <v>582</v>
       </c>
       <c r="H188" t="s">
         <v>14</v>
@@ -10829,19 +10823,19 @@
     </row>
     <row r="189" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B189" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C189">
-        <v>1947</v>
+        <v>1950</v>
       </c>
       <c r="D189" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="E189" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="H189" t="s">
         <v>14</v>
@@ -10849,19 +10843,19 @@
     </row>
     <row r="190" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B190" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C190">
-        <v>1950</v>
+        <v>1947</v>
       </c>
       <c r="D190" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="E190" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="H190" t="s">
         <v>14</v>
@@ -10869,19 +10863,19 @@
     </row>
     <row r="191" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B191" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C191">
         <v>1947</v>
       </c>
       <c r="D191" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="E191" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H191" t="s">
         <v>14</v>
@@ -10889,19 +10883,19 @@
     </row>
     <row r="192" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B192" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C192">
         <v>1947</v>
       </c>
       <c r="D192" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="E192" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="H192" t="s">
         <v>14</v>
@@ -10909,19 +10903,19 @@
     </row>
     <row r="193" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="B193" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C193">
         <v>1947</v>
       </c>
       <c r="D193" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="E193" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="H193" t="s">
         <v>14</v>
@@ -10929,19 +10923,19 @@
     </row>
     <row r="194" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="B194" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C194">
         <v>1947</v>
       </c>
       <c r="D194" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="E194" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="H194" t="s">
         <v>14</v>
@@ -10949,19 +10943,19 @@
     </row>
     <row r="195" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="B195" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C195">
         <v>1947</v>
       </c>
       <c r="D195" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="E195" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="H195" t="s">
         <v>14</v>
@@ -10969,19 +10963,19 @@
     </row>
     <row r="196" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B196" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C196">
-        <v>1947</v>
+        <v>1950</v>
       </c>
       <c r="D196" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="E196" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="H196" t="s">
         <v>14</v>
@@ -10989,19 +10983,19 @@
     </row>
     <row r="197" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="B197" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C197">
         <v>1950</v>
       </c>
       <c r="D197" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="E197" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="H197" t="s">
         <v>14</v>
@@ -11009,19 +11003,19 @@
     </row>
     <row r="198" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B198" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C198">
         <v>1950</v>
       </c>
       <c r="D198" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="E198" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="H198" t="s">
         <v>14</v>
@@ -11029,19 +11023,19 @@
     </row>
     <row r="199" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="B199" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C199">
         <v>1950</v>
       </c>
       <c r="D199" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="E199" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="H199" t="s">
         <v>14</v>
@@ -11049,19 +11043,19 @@
     </row>
     <row r="200" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="B200" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C200">
         <v>1950</v>
       </c>
       <c r="D200" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="E200" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="H200" t="s">
         <v>14</v>
@@ -11069,19 +11063,19 @@
     </row>
     <row r="201" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B201" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C201">
         <v>1950</v>
       </c>
       <c r="D201" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="E201" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="H201" t="s">
         <v>14</v>
@@ -11089,19 +11083,19 @@
     </row>
     <row r="202" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="B202" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C202">
-        <v>1950</v>
+        <v>1924</v>
       </c>
       <c r="D202" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="E202" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H202" t="s">
         <v>14</v>
@@ -11109,19 +11103,19 @@
     </row>
     <row r="203" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="B203" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C203">
-        <v>1924</v>
+        <v>1950</v>
       </c>
       <c r="D203" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="E203" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="H203" t="s">
         <v>14</v>
@@ -11129,19 +11123,22 @@
     </row>
     <row r="204" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="B204" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C204">
-        <v>1950</v>
+        <v>1895</v>
       </c>
       <c r="D204" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="E204" t="s">
-        <v>629</v>
+        <v>630</v>
+      </c>
+      <c r="F204" t="s">
+        <v>13</v>
       </c>
       <c r="H204" t="s">
         <v>14</v>
@@ -11149,22 +11146,19 @@
     </row>
     <row r="205" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="B205" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C205">
-        <v>1895</v>
+        <v>1897</v>
       </c>
       <c r="D205" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="E205" t="s">
-        <v>632</v>
-      </c>
-      <c r="F205" t="s">
-        <v>13</v>
+        <v>633</v>
       </c>
       <c r="H205" t="s">
         <v>14</v>
@@ -11172,19 +11166,19 @@
     </row>
     <row r="206" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B206" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C206">
         <v>1897</v>
       </c>
       <c r="D206" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="E206" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="H206" t="s">
         <v>14</v>
@@ -11192,19 +11186,19 @@
     </row>
     <row r="207" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="B207" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C207">
         <v>1897</v>
       </c>
       <c r="D207" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="E207" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="H207" t="s">
         <v>14</v>
@@ -11212,19 +11206,19 @@
     </row>
     <row r="208" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="B208" t="s">
-        <v>453</v>
+        <v>641</v>
       </c>
       <c r="C208">
-        <v>1897</v>
+        <v>1889</v>
       </c>
       <c r="D208" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="E208" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="H208" t="s">
         <v>14</v>
@@ -11232,19 +11226,19 @@
     </row>
     <row r="209" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="B209" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="C209">
-        <v>1889</v>
+        <v>1900</v>
       </c>
       <c r="D209" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="E209" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="H209" t="s">
         <v>14</v>
@@ -11252,19 +11246,19 @@
     </row>
     <row r="210" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="B210" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="C210">
-        <v>1900</v>
+        <v>1889</v>
       </c>
       <c r="D210" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="E210" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H210" t="s">
         <v>14</v>
@@ -11272,19 +11266,19 @@
     </row>
     <row r="211" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="B211" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="C211">
-        <v>1889</v>
+        <v>1899</v>
       </c>
       <c r="D211" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="E211" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="H211" t="s">
         <v>14</v>
@@ -11292,19 +11286,19 @@
     </row>
     <row r="212" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="B212" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="C212">
-        <v>1899</v>
+        <v>1889</v>
       </c>
       <c r="D212" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="E212" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="H212" t="s">
         <v>14</v>
@@ -11312,19 +11306,22 @@
     </row>
     <row r="213" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="B213" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="C213">
-        <v>1889</v>
+        <v>1899</v>
       </c>
       <c r="D213" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="E213" t="s">
-        <v>657</v>
+        <v>658</v>
+      </c>
+      <c r="F213" t="s">
+        <v>138</v>
       </c>
       <c r="H213" t="s">
         <v>14</v>
@@ -11332,19 +11329,19 @@
     </row>
     <row r="214" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="B214" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="C214">
-        <v>1899</v>
+        <v>1889</v>
       </c>
       <c r="D214" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="E214" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="H214" t="s">
         <v>14</v>
@@ -11352,19 +11349,19 @@
     </row>
     <row r="215" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="B215" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="C215">
         <v>1889</v>
       </c>
       <c r="D215" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="E215" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="H215" t="s">
         <v>14</v>
@@ -11372,19 +11369,19 @@
     </row>
     <row r="216" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="B216" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="C216">
-        <v>1889</v>
+        <v>1900</v>
       </c>
       <c r="D216" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="E216" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="H216" t="s">
         <v>14</v>
@@ -11392,19 +11389,19 @@
     </row>
     <row r="217" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="B217" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="C217">
-        <v>1900</v>
+        <v>1889</v>
       </c>
       <c r="D217" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="E217" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="H217" t="s">
         <v>14</v>
@@ -11412,19 +11409,19 @@
     </row>
     <row r="218" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="B218" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="C218">
-        <v>1889</v>
+        <v>1900</v>
       </c>
       <c r="D218" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="E218" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="H218" t="s">
         <v>14</v>
@@ -11432,19 +11429,19 @@
     </row>
     <row r="219" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="B219" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="C219">
-        <v>1900</v>
+        <v>1899</v>
       </c>
       <c r="D219" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="E219" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="H219" t="s">
         <v>14</v>
@@ -11452,19 +11449,19 @@
     </row>
     <row r="220" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="B220" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="C220">
-        <v>1899</v>
+        <v>1889</v>
       </c>
       <c r="D220" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="E220" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="H220" t="s">
         <v>14</v>
@@ -11472,19 +11469,19 @@
     </row>
     <row r="221" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="B221" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="C221">
-        <v>1889</v>
+        <v>1899</v>
       </c>
       <c r="D221" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="E221" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="H221" t="s">
         <v>14</v>
@@ -11492,19 +11489,19 @@
     </row>
     <row r="222" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="B222" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="C222">
-        <v>1899</v>
+        <v>1889</v>
       </c>
       <c r="D222" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="E222" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="H222" t="s">
         <v>14</v>
@@ -11512,19 +11509,19 @@
     </row>
     <row r="223" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="B223" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="C223">
-        <v>1889</v>
+        <v>1899</v>
       </c>
       <c r="D223" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="E223" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="H223" t="s">
         <v>14</v>
@@ -11532,19 +11529,19 @@
     </row>
     <row r="224" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="B224" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="C224">
-        <v>1899</v>
+        <v>1889</v>
       </c>
       <c r="D224" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="E224" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="H224" t="s">
         <v>14</v>
@@ -11552,19 +11549,19 @@
     </row>
     <row r="225" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="B225" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="C225">
-        <v>1889</v>
+        <v>1920</v>
       </c>
       <c r="D225" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="E225" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="H225" t="s">
         <v>14</v>
@@ -11572,19 +11569,19 @@
     </row>
     <row r="226" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="B226" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="C226">
-        <v>1920</v>
+        <v>1956</v>
       </c>
       <c r="D226" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="E226" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="H226" t="s">
         <v>14</v>
@@ -11592,19 +11589,22 @@
     </row>
     <row r="227" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="B227" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="C227">
-        <v>1956</v>
+        <v>1950</v>
       </c>
       <c r="D227" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="E227" t="s">
-        <v>699</v>
+        <v>700</v>
+      </c>
+      <c r="F227" t="s">
+        <v>138</v>
       </c>
       <c r="H227" t="s">
         <v>14</v>
@@ -11612,19 +11612,22 @@
     </row>
     <row r="228" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="B228" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="C228">
-        <v>1950</v>
+        <v>1956</v>
       </c>
       <c r="D228" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="E228" t="s">
-        <v>702</v>
+        <v>703</v>
+      </c>
+      <c r="F228" t="s">
+        <v>138</v>
       </c>
       <c r="H228" t="s">
         <v>14</v>
@@ -11632,19 +11635,19 @@
     </row>
     <row r="229" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="B229" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="C229">
         <v>1956</v>
       </c>
       <c r="D229" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="E229" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="H229" t="s">
         <v>14</v>
@@ -11652,19 +11655,19 @@
     </row>
     <row r="230" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="B230" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="C230">
-        <v>1956</v>
+        <v>1899</v>
       </c>
       <c r="D230" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="E230" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="H230" t="s">
         <v>14</v>
@@ -11672,19 +11675,19 @@
     </row>
     <row r="231" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="B231" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="C231">
-        <v>1899</v>
+        <v>1890</v>
       </c>
       <c r="D231" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="E231" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="H231" t="s">
         <v>14</v>
@@ -11692,19 +11695,19 @@
     </row>
     <row r="232" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="B232" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="C232">
-        <v>1890</v>
+        <v>1884</v>
       </c>
       <c r="D232" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="E232" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="H232" t="s">
         <v>14</v>
@@ -11712,19 +11715,19 @@
     </row>
     <row r="233" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="B233" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="C233">
-        <v>1884</v>
+        <v>1890</v>
       </c>
       <c r="D233" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="E233" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="H233" t="s">
         <v>14</v>
@@ -11732,19 +11735,19 @@
     </row>
     <row r="234" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="B234" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="C234">
-        <v>1890</v>
+        <v>1923</v>
       </c>
       <c r="D234" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E234" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="H234" t="s">
         <v>14</v>
@@ -11752,19 +11755,19 @@
     </row>
     <row r="235" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="B235" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="C235">
-        <v>1923</v>
+        <v>1921</v>
       </c>
       <c r="D235" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="E235" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="H235" t="s">
         <v>14</v>
@@ -11772,19 +11775,19 @@
     </row>
     <row r="236" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="B236" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="C236">
-        <v>1921</v>
+        <v>1956</v>
       </c>
       <c r="D236" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="E236" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="H236" t="s">
         <v>14</v>
@@ -11792,19 +11795,19 @@
     </row>
     <row r="237" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="B237" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="C237">
-        <v>1956</v>
+        <v>1921</v>
       </c>
       <c r="D237" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="E237" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="H237" t="s">
         <v>14</v>
@@ -11812,19 +11815,19 @@
     </row>
     <row r="238" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="B238" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="C238">
-        <v>1921</v>
+        <v>1950</v>
       </c>
       <c r="D238" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="E238" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="H238" t="s">
         <v>14</v>
@@ -11832,19 +11835,19 @@
     </row>
     <row r="239" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="B239" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="C239">
-        <v>1950</v>
+        <v>1900</v>
       </c>
       <c r="D239" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="E239" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="H239" t="s">
         <v>14</v>
@@ -11852,19 +11855,19 @@
     </row>
     <row r="240" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="B240" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="C240">
-        <v>1900</v>
+        <v>1956</v>
       </c>
       <c r="D240" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="E240" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="H240" t="s">
         <v>14</v>
@@ -11872,19 +11875,19 @@
     </row>
     <row r="241" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="B241" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="C241">
-        <v>1956</v>
+        <v>1900</v>
       </c>
       <c r="D241" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="E241" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="H241" t="s">
         <v>14</v>
@@ -11892,19 +11895,19 @@
     </row>
     <row r="242" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="B242" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="C242">
-        <v>1900</v>
+        <v>1889</v>
       </c>
       <c r="D242" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="E242" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="H242" t="s">
         <v>14</v>
@@ -11912,19 +11915,19 @@
     </row>
     <row r="243" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="B243" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="C243">
-        <v>1889</v>
+        <v>1921</v>
       </c>
       <c r="D243" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="E243" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="H243" t="s">
         <v>14</v>
@@ -11932,19 +11935,19 @@
     </row>
     <row r="244" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="B244" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="C244">
         <v>1921</v>
       </c>
       <c r="D244" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="E244" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="H244" t="s">
         <v>14</v>
@@ -11952,19 +11955,19 @@
     </row>
     <row r="245" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="B245" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="C245">
-        <v>1921</v>
+        <v>1956</v>
       </c>
       <c r="D245" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="E245" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="H245" t="s">
         <v>14</v>
@@ -11972,19 +11975,19 @@
     </row>
     <row r="246" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="B246" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="C246">
         <v>1956</v>
       </c>
       <c r="D246" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="E246" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="H246" t="s">
         <v>14</v>
@@ -11992,19 +11995,19 @@
     </row>
     <row r="247" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="B247" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="C247">
-        <v>1956</v>
+        <v>1950</v>
       </c>
       <c r="D247" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="E247" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="H247" t="s">
         <v>14</v>
@@ -12012,19 +12015,19 @@
     </row>
     <row r="248" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="B248" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="C248">
-        <v>1950</v>
+        <v>1921</v>
       </c>
       <c r="D248" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="E248" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="H248" t="s">
         <v>14</v>
@@ -12032,19 +12035,19 @@
     </row>
     <row r="249" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="B249" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="C249">
         <v>1921</v>
       </c>
       <c r="D249" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="E249" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="H249" t="s">
         <v>14</v>
@@ -12052,19 +12055,19 @@
     </row>
     <row r="250" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="B250" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="C250">
-        <v>1921</v>
+        <v>1956</v>
       </c>
       <c r="D250" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="E250" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="H250" t="s">
         <v>14</v>
@@ -12072,19 +12075,19 @@
     </row>
     <row r="251" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="B251" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="C251">
-        <v>1956</v>
+        <v>1950</v>
       </c>
       <c r="D251" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="E251" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="H251" t="s">
         <v>14</v>
@@ -12092,19 +12095,22 @@
     </row>
     <row r="252" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="B252" t="s">
-        <v>643</v>
+        <v>774</v>
       </c>
       <c r="C252">
-        <v>1950</v>
+        <v>1884</v>
       </c>
       <c r="D252" t="s">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="E252" t="s">
-        <v>774</v>
+        <v>776</v>
+      </c>
+      <c r="F252" t="s">
+        <v>13</v>
       </c>
       <c r="H252" t="s">
         <v>14</v>
@@ -12112,22 +12118,19 @@
     </row>
     <row r="253" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
-        <v>775</v>
+        <v>777</v>
       </c>
       <c r="B253" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="C253">
-        <v>1884</v>
+        <v>1893</v>
       </c>
       <c r="D253" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="E253" t="s">
-        <v>778</v>
-      </c>
-      <c r="F253" t="s">
-        <v>13</v>
+        <v>779</v>
       </c>
       <c r="H253" t="s">
         <v>14</v>
@@ -12135,19 +12138,19 @@
     </row>
     <row r="254" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="B254" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="C254">
-        <v>1893</v>
+        <v>1904</v>
       </c>
       <c r="D254" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="E254" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="H254" t="s">
         <v>14</v>
@@ -12155,19 +12158,19 @@
     </row>
     <row r="255" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="B255" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="C255">
-        <v>1904</v>
+        <v>1916</v>
       </c>
       <c r="D255" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="E255" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="H255" t="s">
         <v>14</v>
@@ -12175,19 +12178,19 @@
     </row>
     <row r="256" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="B256" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="C256">
-        <v>1916</v>
+        <v>1950</v>
       </c>
       <c r="D256" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="E256" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="H256" t="s">
         <v>14</v>
@@ -12195,19 +12198,19 @@
     </row>
     <row r="257" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="B257" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="C257">
-        <v>1950</v>
+        <v>1905</v>
       </c>
       <c r="D257" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="E257" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="H257" t="s">
         <v>14</v>
@@ -12215,19 +12218,19 @@
     </row>
     <row r="258" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="B258" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="C258">
-        <v>1905</v>
+        <v>1917</v>
       </c>
       <c r="D258" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="E258" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="H258" t="s">
         <v>14</v>
@@ -12235,19 +12238,19 @@
     </row>
     <row r="259" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="B259" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="C259">
-        <v>1917</v>
+        <v>1950</v>
       </c>
       <c r="D259" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="E259" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="H259" t="s">
         <v>14</v>
@@ -12255,19 +12258,19 @@
     </row>
     <row r="260" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="B260" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="C260">
-        <v>1950</v>
+        <v>1917</v>
       </c>
       <c r="D260" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="E260" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="H260" t="s">
         <v>14</v>
@@ -12275,19 +12278,19 @@
     </row>
     <row r="261" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="B261" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="C261">
-        <v>1917</v>
+        <v>1893</v>
       </c>
       <c r="D261" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="E261" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H261" t="s">
         <v>14</v>
@@ -12295,19 +12298,19 @@
     </row>
     <row r="262" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="B262" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="C262">
-        <v>1893</v>
+        <v>1905</v>
       </c>
       <c r="D262" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="E262" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="H262" t="s">
         <v>14</v>
@@ -12315,19 +12318,19 @@
     </row>
     <row r="263" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="B263" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="C263">
-        <v>1905</v>
+        <v>1950</v>
       </c>
       <c r="D263" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="E263" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="H263" t="s">
         <v>14</v>
@@ -12335,19 +12338,19 @@
     </row>
     <row r="264" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="B264" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="C264">
-        <v>1950</v>
+        <v>1919</v>
       </c>
       <c r="D264" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="E264" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="H264" t="s">
         <v>14</v>
@@ -12355,41 +12358,21 @@
     </row>
     <row r="265" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B265" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="C265">
-        <v>1919</v>
+        <v>1950</v>
       </c>
       <c r="D265" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="E265" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="H265" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="266" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A266" t="s">
-        <v>815</v>
-      </c>
-      <c r="B266" t="s">
-        <v>776</v>
-      </c>
-      <c r="C266">
-        <v>1950</v>
-      </c>
-      <c r="D266" t="s">
-        <v>816</v>
-      </c>
-      <c r="E266" t="s">
-        <v>817</v>
-      </c>
-      <c r="H266" t="s">
         <v>14</v>
       </c>
     </row>
@@ -12409,7 +12392,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>0</v>
@@ -12417,7 +12400,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="B2" t="s">
         <v>301</v>
@@ -12425,7 +12408,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="B3" t="s">
         <v>304</v>
@@ -12433,7 +12416,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="B4" t="s">
         <v>286</v>
@@ -12441,7 +12424,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="B5" t="s">
         <v>292</v>
@@ -12449,7 +12432,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="B6" t="s">
         <v>282</v>
@@ -12457,7 +12440,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="B7" t="s">
         <v>289</v>
@@ -12465,7 +12448,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="B8" t="s">
         <v>295</v>
@@ -12473,7 +12456,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="B9" t="s">
         <v>298</v>
@@ -12481,7 +12464,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="B10" t="s">
         <v>307</v>
@@ -12489,7 +12472,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="B11" t="s">
         <v>310</v>
@@ -12497,7 +12480,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
       <c r="B12" t="s">
         <v>313</v>
@@ -12505,7 +12488,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
       <c r="B13" t="s">
         <v>316</v>
@@ -12513,7 +12496,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="B14" t="s">
         <v>175</v>
@@ -12521,7 +12504,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="B15" t="s">
         <v>194</v>
@@ -12529,7 +12512,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>850</v>
+        <v>848</v>
       </c>
       <c r="B16" t="s">
         <v>179</v>
@@ -12537,7 +12520,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>850</v>
+        <v>848</v>
       </c>
       <c r="B17" t="s">
         <v>182</v>
@@ -12545,7 +12528,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>850</v>
+        <v>848</v>
       </c>
       <c r="B18" t="s">
         <v>185</v>
@@ -12553,7 +12536,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>850</v>
+        <v>848</v>
       </c>
       <c r="B19" t="s">
         <v>188</v>
@@ -12561,7 +12544,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>850</v>
+        <v>848</v>
       </c>
       <c r="B20" t="s">
         <v>191</v>
@@ -12569,7 +12552,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
       <c r="B21" t="s">
         <v>197</v>
@@ -12577,7 +12560,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
       <c r="B22" t="s">
         <v>200</v>
@@ -12585,7 +12568,7 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>856</v>
+        <v>854</v>
       </c>
       <c r="B23" t="s">
         <v>203</v>
@@ -12593,7 +12576,7 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>856</v>
+        <v>854</v>
       </c>
       <c r="B24" t="s">
         <v>206</v>
@@ -12601,7 +12584,7 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>856</v>
+        <v>854</v>
       </c>
       <c r="B25" t="s">
         <v>209</v>
@@ -12609,7 +12592,7 @@
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="B26" t="s">
         <v>9</v>
@@ -12617,7 +12600,7 @@
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="B27" t="s">
         <v>32</v>
@@ -12625,7 +12608,7 @@
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="B28" t="s">
         <v>47</v>
@@ -12633,7 +12616,7 @@
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="B29" t="s">
         <v>15</v>
@@ -12641,7 +12624,7 @@
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="B30" t="s">
         <v>35</v>
@@ -12649,7 +12632,7 @@
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="B31" t="s">
         <v>50</v>
@@ -12657,7 +12640,7 @@
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="B32" t="s">
         <v>65</v>
@@ -12665,7 +12648,7 @@
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="B33" t="s">
         <v>18</v>
@@ -12673,7 +12656,7 @@
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="B34" t="s">
         <v>22</v>
@@ -12681,7 +12664,7 @@
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="B35" t="s">
         <v>29</v>
@@ -12689,7 +12672,7 @@
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="B36" t="s">
         <v>32</v>
@@ -12697,7 +12680,7 @@
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="B37" t="s">
         <v>44</v>
@@ -12705,7 +12688,7 @@
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="B38" t="s">
         <v>47</v>
@@ -12713,7 +12696,7 @@
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="B39" t="s">
         <v>59</v>
@@ -12721,7 +12704,7 @@
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="B40" t="s">
         <v>62</v>
@@ -12729,7 +12712,7 @@
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="B41" t="s">
         <v>26</v>
@@ -12737,7 +12720,7 @@
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="B42" t="s">
         <v>41</v>
@@ -12745,7 +12728,7 @@
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="B43" t="s">
         <v>56</v>
@@ -12753,7 +12736,7 @@
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="B44" t="s">
         <v>71</v>
@@ -12761,7 +12744,7 @@
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="B45" t="s">
         <v>74</v>
@@ -12769,7 +12752,7 @@
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="B46" t="s">
         <v>77</v>
@@ -12777,7 +12760,7 @@
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="B47" t="s">
         <v>38</v>
@@ -12785,7 +12768,7 @@
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="B48" t="s">
         <v>53</v>
@@ -12793,7 +12776,7 @@
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="B49" t="s">
         <v>68</v>
@@ -12801,7 +12784,7 @@
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>903</v>
+        <v>901</v>
       </c>
       <c r="B50" t="s">
         <v>80</v>
@@ -12809,7 +12792,7 @@
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>903</v>
+        <v>901</v>
       </c>
       <c r="B51" t="s">
         <v>111</v>
@@ -12817,7 +12800,7 @@
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>904</v>
+        <v>902</v>
       </c>
       <c r="B52" t="s">
         <v>84</v>
@@ -12825,7 +12808,7 @@
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>904</v>
+        <v>902</v>
       </c>
       <c r="B53" t="s">
         <v>108</v>
@@ -12833,7 +12816,7 @@
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>904</v>
+        <v>902</v>
       </c>
       <c r="B54" t="s">
         <v>114</v>
@@ -12841,7 +12824,7 @@
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>904</v>
+        <v>902</v>
       </c>
       <c r="B55" t="s">
         <v>123</v>
@@ -12849,7 +12832,7 @@
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>905</v>
+        <v>903</v>
       </c>
       <c r="B56" t="s">
         <v>117</v>
@@ -12857,7 +12840,7 @@
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>906</v>
+        <v>904</v>
       </c>
       <c r="B57" t="s">
         <v>154</v>
@@ -12865,7 +12848,7 @@
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>906</v>
+        <v>904</v>
       </c>
       <c r="B58" t="s">
         <v>157</v>
@@ -12873,7 +12856,7 @@
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>906</v>
+        <v>904</v>
       </c>
       <c r="B59" t="s">
         <v>163</v>
@@ -12881,7 +12864,7 @@
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>906</v>
+        <v>904</v>
       </c>
       <c r="B60" t="s">
         <v>166</v>
@@ -12889,7 +12872,7 @@
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>908</v>
+        <v>906</v>
       </c>
       <c r="B61" t="s">
         <v>87</v>
@@ -12897,7 +12880,7 @@
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>908</v>
+        <v>906</v>
       </c>
       <c r="B62" t="s">
         <v>93</v>
@@ -12905,7 +12888,7 @@
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>908</v>
+        <v>906</v>
       </c>
       <c r="B63" t="s">
         <v>99</v>
@@ -12913,7 +12896,7 @@
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
       <c r="B64" t="s">
         <v>90</v>
@@ -12921,7 +12904,7 @@
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
       <c r="B65" t="s">
         <v>96</v>
@@ -12929,7 +12912,7 @@
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
       <c r="B66" t="s">
         <v>102</v>
@@ -12937,7 +12920,7 @@
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
       <c r="B67" t="s">
         <v>120</v>
@@ -12945,7 +12928,7 @@
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
       <c r="B68" t="s">
         <v>129</v>
@@ -12953,7 +12936,7 @@
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
       <c r="B69" t="s">
         <v>135</v>
@@ -12961,7 +12944,7 @@
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
       <c r="B70" t="s">
         <v>142</v>
@@ -12969,7 +12952,7 @@
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="B71" t="s">
         <v>148</v>
@@ -12977,7 +12960,7 @@
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="B72" t="s">
         <v>132</v>
@@ -12985,7 +12968,7 @@
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="B73" t="s">
         <v>139</v>
@@ -12993,7 +12976,7 @@
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="B74" t="s">
         <v>145</v>
@@ -13001,7 +12984,7 @@
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
       <c r="B75" t="s">
         <v>151</v>
@@ -13009,7 +12992,7 @@
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
       <c r="B76" t="s">
         <v>132</v>
@@ -13017,7 +13000,7 @@
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
       <c r="B77" t="s">
         <v>139</v>
@@ -13025,7 +13008,7 @@
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
       <c r="B78" t="s">
         <v>145</v>
@@ -13033,7 +13016,7 @@
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>914</v>
+        <v>912</v>
       </c>
       <c r="B79" t="s">
         <v>160</v>
@@ -13041,7 +13024,7 @@
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>914</v>
+        <v>912</v>
       </c>
       <c r="B80" t="s">
         <v>169</v>
@@ -13049,7 +13032,7 @@
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>915</v>
+        <v>913</v>
       </c>
       <c r="B81" t="s">
         <v>172</v>
@@ -13057,7 +13040,7 @@
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>916</v>
+        <v>914</v>
       </c>
       <c r="B82" t="s">
         <v>126</v>
@@ -13065,7 +13048,7 @@
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>916</v>
+        <v>914</v>
       </c>
       <c r="B83" t="s">
         <v>105</v>
@@ -13073,7 +13056,7 @@
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="B84" t="s">
         <v>255</v>
@@ -13081,7 +13064,7 @@
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="B85" t="s">
         <v>252</v>
@@ -13089,7 +13072,7 @@
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
       <c r="B86" t="s">
         <v>261</v>
@@ -13097,7 +13080,7 @@
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
       <c r="B87" t="s">
         <v>222</v>
@@ -13105,7 +13088,7 @@
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
       <c r="B88" t="s">
         <v>231</v>
@@ -13113,7 +13096,7 @@
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
       <c r="B89" t="s">
         <v>240</v>
@@ -13121,7 +13104,7 @@
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>921</v>
+        <v>919</v>
       </c>
       <c r="B90" t="s">
         <v>258</v>
@@ -13129,7 +13112,7 @@
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="B91" t="s">
         <v>212</v>
@@ -13137,7 +13120,7 @@
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="B92" t="s">
         <v>267</v>
@@ -13145,7 +13128,7 @@
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="B93" t="s">
         <v>270</v>
@@ -13153,7 +13136,7 @@
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="B94" t="s">
         <v>273</v>
@@ -13161,7 +13144,7 @@
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="B95" t="s">
         <v>276</v>
@@ -13169,7 +13152,7 @@
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
       <c r="B96" t="s">
         <v>216</v>
@@ -13177,7 +13160,7 @@
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
       <c r="B97" t="s">
         <v>264</v>
@@ -13185,7 +13168,7 @@
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>924</v>
+        <v>922</v>
       </c>
       <c r="B98" t="s">
         <v>243</v>
@@ -13193,7 +13176,7 @@
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="B99" t="s">
         <v>219</v>
@@ -13201,7 +13184,7 @@
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="B100" t="s">
         <v>225</v>
@@ -13209,7 +13192,7 @@
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="B101" t="s">
         <v>234</v>
@@ -13217,7 +13200,7 @@
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="B102" t="s">
         <v>246</v>
@@ -13225,7 +13208,7 @@
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="B103" t="s">
         <v>228</v>
@@ -13233,7 +13216,7 @@
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="B104" t="s">
         <v>237</v>
@@ -13241,7 +13224,7 @@
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="B105" t="s">
         <v>249</v>
@@ -13249,7 +13232,7 @@
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="B106" t="s">
         <v>279</v>
@@ -13257,7 +13240,7 @@
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
       <c r="B107" t="s">
         <v>350</v>
@@ -13265,7 +13248,7 @@
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
       <c r="B108" t="s">
         <v>357</v>
@@ -13273,7 +13256,7 @@
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="B109" t="s">
         <v>354</v>
@@ -13281,7 +13264,7 @@
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="B110" t="s">
         <v>360</v>
@@ -13289,7 +13272,7 @@
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
       <c r="B111" t="s">
         <v>372</v>
@@ -13297,7 +13280,7 @@
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
       <c r="B112" t="s">
         <v>374</v>
@@ -13305,7 +13288,7 @@
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>931</v>
+        <v>929</v>
       </c>
       <c r="B113" t="s">
         <v>366</v>
@@ -13313,7 +13296,7 @@
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>932</v>
+        <v>930</v>
       </c>
       <c r="B114" t="s">
         <v>369</v>
@@ -13321,7 +13304,7 @@
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="B115" t="s">
         <v>380</v>
@@ -13329,7 +13312,7 @@
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="B116" t="s">
         <v>383</v>
@@ -13337,7 +13320,7 @@
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>934</v>
+        <v>932</v>
       </c>
       <c r="B117" t="s">
         <v>377</v>
@@ -13345,7 +13328,7 @@
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>934</v>
+        <v>932</v>
       </c>
       <c r="B118" t="s">
         <v>386</v>
@@ -13353,7 +13336,7 @@
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>935</v>
+        <v>933</v>
       </c>
       <c r="B119" t="s">
         <v>363</v>
@@ -13361,7 +13344,7 @@
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>936</v>
+        <v>934</v>
       </c>
       <c r="B120" t="s">
         <v>323</v>
@@ -13369,7 +13352,7 @@
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>936</v>
+        <v>934</v>
       </c>
       <c r="B121" t="s">
         <v>326</v>
@@ -13377,7 +13360,7 @@
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>939</v>
+        <v>937</v>
       </c>
       <c r="B122" t="s">
         <v>338</v>
@@ -13385,7 +13368,7 @@
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>939</v>
+        <v>937</v>
       </c>
       <c r="B123" t="s">
         <v>344</v>
@@ -13393,7 +13376,7 @@
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>939</v>
+        <v>937</v>
       </c>
       <c r="B124" t="s">
         <v>332</v>
@@ -13401,7 +13384,7 @@
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>942</v>
+        <v>940</v>
       </c>
       <c r="B125" t="s">
         <v>341</v>
@@ -13409,7 +13392,7 @@
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>942</v>
+        <v>940</v>
       </c>
       <c r="B126" t="s">
         <v>347</v>
@@ -13417,7 +13400,7 @@
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>942</v>
+        <v>940</v>
       </c>
       <c r="B127" t="s">
         <v>335</v>
@@ -13425,7 +13408,7 @@
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>945</v>
+        <v>943</v>
       </c>
       <c r="B128" t="s">
         <v>319</v>
@@ -13433,7 +13416,7 @@
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>945</v>
+        <v>943</v>
       </c>
       <c r="B129" t="s">
         <v>329</v>
@@ -13441,7 +13424,7 @@
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="B130" t="s">
         <v>389</v>
@@ -13449,7 +13432,7 @@
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="B131" t="s">
         <v>62</v>
@@ -13457,7 +13440,7 @@
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="B132" t="s">
         <v>392</v>
@@ -13465,7 +13448,7 @@
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>905</v>
+        <v>903</v>
       </c>
       <c r="B133" t="s">
         <v>395</v>
@@ -13473,7 +13456,7 @@
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>906</v>
+        <v>904</v>
       </c>
       <c r="B134" t="s">
         <v>398</v>
@@ -13481,7 +13464,7 @@
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>906</v>
+        <v>904</v>
       </c>
       <c r="B135" t="s">
         <v>401</v>
@@ -13489,7 +13472,7 @@
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>906</v>
+        <v>904</v>
       </c>
       <c r="B136" t="s">
         <v>404</v>
@@ -13497,7 +13480,7 @@
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>906</v>
+        <v>904</v>
       </c>
       <c r="B137" t="s">
         <v>407</v>
@@ -13505,7 +13488,7 @@
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>907</v>
+        <v>905</v>
       </c>
       <c r="B138" t="s">
         <v>404</v>
@@ -13513,7 +13496,7 @@
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>907</v>
+        <v>905</v>
       </c>
       <c r="B139" t="s">
         <v>407</v>
@@ -13521,7 +13504,7 @@
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>908</v>
+        <v>906</v>
       </c>
       <c r="B140" t="s">
         <v>410</v>
@@ -13529,7 +13512,7 @@
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
       <c r="B141" t="s">
         <v>413</v>
@@ -13537,7 +13520,7 @@
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
       <c r="B142" t="s">
         <v>416</v>
@@ -13545,7 +13528,7 @@
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
       <c r="B143" t="s">
         <v>419</v>
@@ -13553,1050 +13536,1050 @@
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
       <c r="B144" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
       <c r="B145" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
       <c r="B146" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>916</v>
+        <v>914</v>
       </c>
       <c r="B147" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
       <c r="B148" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="B149" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
       <c r="B150" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>931</v>
+        <v>929</v>
       </c>
       <c r="B151" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>932</v>
+        <v>930</v>
       </c>
       <c r="B152" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>932</v>
+        <v>930</v>
       </c>
       <c r="B153" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>948</v>
+        <v>946</v>
       </c>
       <c r="B154" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>948</v>
+        <v>946</v>
       </c>
       <c r="B155" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="B156" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>954</v>
+        <v>952</v>
       </c>
       <c r="B157" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>954</v>
+        <v>952</v>
       </c>
       <c r="B158" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>957</v>
+        <v>955</v>
       </c>
       <c r="B159" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>959</v>
+        <v>957</v>
       </c>
       <c r="B160" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>959</v>
+        <v>957</v>
       </c>
       <c r="B161" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>961</v>
+        <v>959</v>
       </c>
       <c r="B162" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>963</v>
+        <v>961</v>
       </c>
       <c r="B163" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>965</v>
+        <v>963</v>
       </c>
       <c r="B164" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>968</v>
+        <v>966</v>
       </c>
       <c r="B165" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>971</v>
+        <v>969</v>
       </c>
       <c r="B166" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>973</v>
+        <v>971</v>
       </c>
       <c r="B167" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>973</v>
+        <v>971</v>
       </c>
       <c r="B168" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>976</v>
+        <v>974</v>
       </c>
       <c r="B169" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>976</v>
+        <v>974</v>
       </c>
       <c r="B170" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>978</v>
+        <v>976</v>
       </c>
       <c r="B171" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
       <c r="B172" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
       <c r="B173" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>984</v>
+        <v>982</v>
       </c>
       <c r="B174" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>984</v>
+        <v>982</v>
       </c>
       <c r="B175" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>987</v>
+        <v>985</v>
       </c>
       <c r="B176" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>990</v>
+        <v>988</v>
       </c>
       <c r="B177" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>990</v>
+        <v>988</v>
       </c>
       <c r="B178" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="B179" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="B180" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="B181" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="B182" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
       <c r="B183" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="B184" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>1041</v>
+        <v>1039</v>
       </c>
       <c r="B185" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>1045</v>
+        <v>1043</v>
       </c>
       <c r="B186" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>1047</v>
+        <v>1045</v>
       </c>
       <c r="B187" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>1049</v>
+        <v>1047</v>
       </c>
       <c r="B188" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>1049</v>
+        <v>1047</v>
       </c>
       <c r="B189" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="B190" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>954</v>
+        <v>952</v>
       </c>
       <c r="B191" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>1004</v>
+        <v>1002</v>
       </c>
       <c r="B192" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="B193" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="B194" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
       <c r="B195" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
       <c r="B196" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
       <c r="B197" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
       <c r="B198" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
       <c r="B199" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="B200" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="B201" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
       <c r="B202" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
       <c r="B203" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
       <c r="B204" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
       <c r="B205" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="B206" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="B207" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>1028</v>
+        <v>1026</v>
       </c>
       <c r="B208" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>1028</v>
+        <v>1026</v>
       </c>
       <c r="B209" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>1032</v>
+        <v>1030</v>
       </c>
       <c r="B210" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>1032</v>
+        <v>1030</v>
       </c>
       <c r="B211" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
     </row>
     <row r="212" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="B212" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
     </row>
     <row r="213" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="B213" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
     </row>
     <row r="214" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>1038</v>
+        <v>1036</v>
       </c>
       <c r="B214" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
     </row>
     <row r="215" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>1038</v>
+        <v>1036</v>
       </c>
       <c r="B215" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
     </row>
     <row r="216" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
       <c r="B216" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
     </row>
     <row r="217" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="B217" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
     </row>
     <row r="218" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="B218" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
     </row>
     <row r="219" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="B219" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
     </row>
     <row r="220" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="B220" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="B221" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
     </row>
     <row r="222" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
       <c r="B222" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
     </row>
     <row r="223" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
       <c r="B223" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
     </row>
     <row r="224" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
       <c r="B224" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
     </row>
     <row r="225" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
       <c r="B225" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
     </row>
     <row r="226" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>873</v>
+        <v>871</v>
       </c>
       <c r="B226" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
     </row>
     <row r="227" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>876</v>
+        <v>874</v>
       </c>
       <c r="B227" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
     </row>
     <row r="228" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>876</v>
+        <v>874</v>
       </c>
       <c r="B228" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
     </row>
     <row r="229" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="B229" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
     </row>
     <row r="230" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="B230" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
     </row>
     <row r="231" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>882</v>
+        <v>880</v>
       </c>
       <c r="B231" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
     </row>
     <row r="232" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>882</v>
+        <v>880</v>
       </c>
       <c r="B232" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
     </row>
     <row r="233" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="B233" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
     </row>
     <row r="234" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="B234" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
     </row>
     <row r="235" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
       <c r="B235" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
     </row>
     <row r="236" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
       <c r="B236" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
     </row>
     <row r="237" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="B237" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
     </row>
     <row r="238" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="B238" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
     </row>
     <row r="239" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="B239" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
     </row>
     <row r="240" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="B240" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
     </row>
     <row r="241" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>897</v>
+        <v>895</v>
       </c>
       <c r="B241" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
     </row>
     <row r="242" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>900</v>
+        <v>898</v>
       </c>
       <c r="B242" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
     </row>
     <row r="243" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>1051</v>
+        <v>1049</v>
       </c>
       <c r="B243" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
     </row>
     <row r="244" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="B244" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
     </row>
     <row r="245" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>1056</v>
+        <v>1054</v>
       </c>
       <c r="B245" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
     </row>
     <row r="246" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>1056</v>
+        <v>1054</v>
       </c>
       <c r="B246" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
     </row>
     <row r="247" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="B247" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
     </row>
     <row r="248" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="B248" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
     </row>
     <row r="249" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
-        <v>1060</v>
+        <v>1058</v>
       </c>
       <c r="B249" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
     </row>
     <row r="250" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>1060</v>
+        <v>1058</v>
       </c>
       <c r="B250" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
     </row>
     <row r="251" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
-        <v>1060</v>
+        <v>1058</v>
       </c>
       <c r="B251" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
     </row>
     <row r="252" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
-        <v>1060</v>
+        <v>1058</v>
       </c>
       <c r="B252" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
     </row>
     <row r="253" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
-        <v>1062</v>
+        <v>1060</v>
       </c>
       <c r="B253" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
     </row>
     <row r="254" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
-        <v>1062</v>
+        <v>1060</v>
       </c>
       <c r="B254" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
     </row>
     <row r="255" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
-        <v>1062</v>
+        <v>1060</v>
       </c>
       <c r="B255" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
     </row>
     <row r="256" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>1065</v>
+        <v>1063</v>
       </c>
       <c r="B256" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
     </row>
     <row r="257" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>1065</v>
+        <v>1063</v>
       </c>
       <c r="B257" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
     </row>
     <row r="258" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
-        <v>873</v>
+        <v>871</v>
       </c>
       <c r="B258" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
     </row>
     <row r="259" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>873</v>
+        <v>871</v>
       </c>
       <c r="B259" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
     </row>
     <row r="260" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
-        <v>873</v>
+        <v>871</v>
       </c>
       <c r="B260" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
     </row>
     <row r="261" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="B261" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
     </row>
     <row r="262" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="B262" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
     </row>
     <row r="263" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="B263" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
     </row>
     <row r="264" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="B264" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
     </row>
     <row r="265" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="B265" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
     </row>
     <row r="266" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
-        <v>1070</v>
+        <v>1068</v>
       </c>
       <c r="B266" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
     </row>
     <row r="267" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
-        <v>1070</v>
+        <v>1068</v>
       </c>
       <c r="B267" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
     </row>
     <row r="268" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
-        <v>1070</v>
+        <v>1068</v>
       </c>
       <c r="B268" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
     </row>
     <row r="269" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
-        <v>1072</v>
+        <v>1070</v>
       </c>
       <c r="B269" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
     </row>
     <row r="270" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
-        <v>1072</v>
+        <v>1070</v>
       </c>
       <c r="B270" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
     </row>
     <row r="271" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
-        <v>1072</v>
+        <v>1070</v>
       </c>
       <c r="B271" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
     </row>
     <row r="272" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
-        <v>1072</v>
+        <v>1070</v>
       </c>
       <c r="B272" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
     </row>
     <row r="273" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
-        <v>1074</v>
+        <v>1072</v>
       </c>
       <c r="B273" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
     </row>
     <row r="274" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
-        <v>1074</v>
+        <v>1072</v>
       </c>
       <c r="B274" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
     </row>
   </sheetData>
@@ -14616,207 +14599,207 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
+        <v>825</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1074</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>1075</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>1076</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>827</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1076</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>1077</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>1078</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>829</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="B2" t="s">
+        <v>1077</v>
+      </c>
+      <c r="C2" t="s">
+        <v>1078</v>
+      </c>
+      <c r="D2" t="s">
         <v>1079</v>
-      </c>
-      <c r="C2" t="s">
-        <v>1080</v>
-      </c>
-      <c r="D2" t="s">
-        <v>1081</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="B3" t="s">
-        <v>1082</v>
+        <v>1080</v>
       </c>
       <c r="C3" t="s">
-        <v>1080</v>
+        <v>1078</v>
       </c>
       <c r="D3" t="s">
-        <v>1081</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="B4" t="s">
-        <v>1083</v>
+        <v>1081</v>
       </c>
       <c r="C4" t="s">
-        <v>1080</v>
+        <v>1078</v>
       </c>
       <c r="D4" t="s">
-        <v>1081</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="B5" t="s">
-        <v>1084</v>
+        <v>1082</v>
       </c>
       <c r="C5" t="s">
-        <v>1080</v>
+        <v>1078</v>
       </c>
       <c r="D5" t="s">
-        <v>1081</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>905</v>
+        <v>903</v>
       </c>
       <c r="B6" t="s">
-        <v>1085</v>
+        <v>1083</v>
       </c>
       <c r="C6" t="s">
-        <v>1080</v>
+        <v>1078</v>
       </c>
       <c r="D6" t="s">
-        <v>1081</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
       <c r="B7" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
       <c r="C7" t="s">
-        <v>1080</v>
+        <v>1078</v>
       </c>
       <c r="D7" t="s">
-        <v>1081</v>
+        <v>1079</v>
       </c>
       <c r="E7" t="s">
-        <v>1087</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
       <c r="B8" t="s">
-        <v>1088</v>
+        <v>1086</v>
       </c>
       <c r="C8" t="s">
-        <v>1080</v>
+        <v>1078</v>
       </c>
       <c r="D8" t="s">
-        <v>1081</v>
+        <v>1079</v>
       </c>
       <c r="E8" t="s">
-        <v>1087</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
       <c r="B9" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="C9" t="s">
-        <v>1080</v>
+        <v>1078</v>
       </c>
       <c r="D9" t="s">
-        <v>1081</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>1090</v>
+        <v>1088</v>
       </c>
       <c r="B10" t="s">
-        <v>1091</v>
+        <v>1089</v>
       </c>
       <c r="C10" t="s">
-        <v>1080</v>
+        <v>1078</v>
       </c>
       <c r="D10" t="s">
-        <v>1081</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="B11" t="s">
-        <v>1092</v>
+        <v>1090</v>
       </c>
       <c r="C11" t="s">
-        <v>1080</v>
+        <v>1078</v>
       </c>
       <c r="D11" t="s">
-        <v>1081</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="B12" t="s">
-        <v>1093</v>
+        <v>1091</v>
       </c>
       <c r="C12" t="s">
-        <v>1080</v>
+        <v>1078</v>
       </c>
       <c r="D12" t="s">
-        <v>1081</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="B13" t="s">
-        <v>1094</v>
+        <v>1092</v>
       </c>
       <c r="C13" t="s">
-        <v>1080</v>
+        <v>1078</v>
       </c>
       <c r="D13" t="s">
-        <v>1081</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="B14" t="s">
-        <v>1095</v>
+        <v>1093</v>
       </c>
       <c r="C14" t="s">
-        <v>1080</v>
+        <v>1078</v>
       </c>
       <c r="D14" t="s">
-        <v>1081</v>
+        <v>1079</v>
       </c>
     </row>
   </sheetData>

--- a/data/atlas.xlsx
+++ b/data/atlas.xlsx
@@ -8,23 +8,24 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SOCIOLOGY\github\websites\mgi_atlas_website\mgi_atlas\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA8A8EBB-6963-44CC-85D5-B33225DE1279}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A7B9CEB-43CF-49AF-B1C9-02F89F6DF8D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
     <sheet name="Points" sheetId="2" r:id="rId2"/>
     <sheet name="Maps" sheetId="3" r:id="rId3"/>
-    <sheet name="Links" sheetId="4" r:id="rId4"/>
-    <sheet name="Review" sheetId="5" r:id="rId5"/>
+    <sheet name="Total Maps" sheetId="6" r:id="rId4"/>
+    <sheet name="Links" sheetId="4" r:id="rId5"/>
+    <sheet name="Review" sheetId="5" r:id="rId6"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2744" uniqueCount="1094">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2756" uniqueCount="1106">
   <si>
     <t>map_id</t>
   </si>
@@ -3306,6 +3307,42 @@
   </si>
   <si>
     <t>03573_04_1915-0362</t>
+  </si>
+  <si>
+    <t>region</t>
+  </si>
+  <si>
+    <t>n_maps</t>
+  </si>
+  <si>
+    <t>chicagoland</t>
+  </si>
+  <si>
+    <t>providence area</t>
+  </si>
+  <si>
+    <t>baltimore</t>
+  </si>
+  <si>
+    <t>seattle</t>
+  </si>
+  <si>
+    <t>san francisco</t>
+  </si>
+  <si>
+    <t>oakland</t>
+  </si>
+  <si>
+    <t>kansas city</t>
+  </si>
+  <si>
+    <t>minneapolis</t>
+  </si>
+  <si>
+    <t>new orleans</t>
+  </si>
+  <si>
+    <t>cleveland</t>
   </si>
 </sst>
 </file>
@@ -12382,6 +12419,104 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F4E8AC8-E3AF-4EC8-A88D-6EBE773C1BBE}">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>1094</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>1096</v>
+      </c>
+      <c r="B2">
+        <v>16319</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>1097</v>
+      </c>
+      <c r="B3">
+        <v>2497</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>1098</v>
+      </c>
+      <c r="B4">
+        <v>5099</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>1099</v>
+      </c>
+      <c r="B5">
+        <v>2318</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>1100</v>
+      </c>
+      <c r="B6">
+        <v>3475</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>1101</v>
+      </c>
+      <c r="B7">
+        <v>3326</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>1102</v>
+      </c>
+      <c r="B8">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>1103</v>
+      </c>
+      <c r="B9">
+        <v>3396</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>1104</v>
+      </c>
+      <c r="B10">
+        <v>2944</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>1105</v>
+      </c>
+      <c r="B11">
+        <v>6793</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:B274"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -14587,7 +14722,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:E14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
